--- a/Lewitus_etal_2014/pbio.1002000.s013.xlsx
+++ b/Lewitus_etal_2014/pbio.1002000.s013.xlsx
@@ -1,16 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="20910"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10920"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alleninstitute.sharepoint.com/sites/MammalianM1/Shared Documents/General/Species/Evo-M1-Trait-Data/Lewitus_etal_2014/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="12" documentId="11_4926A3AA9C8272EF334B9A302C490626388AC9B9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{07B561D9-369A-E842-9E2C-6DF98487026F}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="240" windowWidth="25360" windowHeight="14000" tabRatio="500"/>
+    <workbookView xWindow="34940" yWindow="-5860" windowWidth="15460" windowHeight="28200" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="140000" concurrentCalc="0"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$AN$106</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{7523E5D3-25F3-A5E0-1632-64F254C22452}">
       <mx:ArchID Flags="2"/>
     </ext>
@@ -496,8 +516,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -533,13 +553,26 @@
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -554,7 +587,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -570,12 +603,26 @@
     <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -900,11 +947,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:AN106"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:40">
+    <row r="1" spans="1:40" ht="18" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -948,7 +996,7 @@
       <c r="AM1" s="3"/>
       <c r="AN1" s="3"/>
     </row>
-    <row r="2" spans="1:40">
+    <row r="2" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
@@ -1070,7 +1118,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:40">
+    <row r="3" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>41</v>
       </c>
@@ -1192,7 +1240,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:40">
+    <row r="4" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>43</v>
       </c>
@@ -1314,7 +1362,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:40">
+    <row r="5" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>44</v>
       </c>
@@ -1436,7 +1484,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:40">
+    <row r="6" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>45</v>
       </c>
@@ -1558,7 +1606,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:40">
+    <row r="7" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
         <v>46</v>
       </c>
@@ -1680,7 +1728,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:40">
+    <row r="8" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
         <v>47</v>
       </c>
@@ -1802,7 +1850,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:40">
+    <row r="9" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>48</v>
       </c>
@@ -1924,7 +1972,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:40">
+    <row r="10" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
         <v>49</v>
       </c>
@@ -2046,7 +2094,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:40">
+    <row r="11" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
         <v>50</v>
       </c>
@@ -2168,215 +2216,215 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:40">
+    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="B12" s="5">
-        <v>7421.4</v>
+        <v>783.6</v>
       </c>
       <c r="C12" s="5">
-        <v>105.65</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E12" s="5">
-        <v>77141</v>
+        <v>17.399999999999999</v>
+      </c>
+      <c r="D12" s="5">
+        <v>10.1</v>
+      </c>
+      <c r="E12" s="7">
+        <v>9950</v>
       </c>
       <c r="F12" s="5">
-        <v>1.91</v>
+        <v>1.31</v>
       </c>
       <c r="G12" s="5">
-        <v>561</v>
+        <v>105</v>
       </c>
       <c r="H12" s="5">
-        <v>21.6</v>
+        <v>25.25</v>
       </c>
       <c r="I12" s="5">
-        <v>36</v>
+        <v>28.56666667</v>
       </c>
       <c r="J12" s="5">
-        <v>1095</v>
+        <v>868.90277790000005</v>
       </c>
       <c r="K12" s="6">
-        <v>1246.07</v>
+        <v>821</v>
       </c>
       <c r="L12" s="6">
-        <v>1246.07</v>
+        <v>730</v>
       </c>
       <c r="M12" s="6">
-        <v>167</v>
+        <v>137.5</v>
       </c>
       <c r="N12" s="5">
         <v>1</v>
       </c>
-      <c r="O12" s="5" t="s">
-        <v>42</v>
+      <c r="O12" s="5">
+        <v>1.4</v>
       </c>
       <c r="P12" s="6">
+        <v>269</v>
+      </c>
+      <c r="Q12" s="6">
+        <v>110.33333330000001</v>
+      </c>
+      <c r="R12" s="5">
+        <v>91.25</v>
+      </c>
+      <c r="S12" s="5">
+        <v>360</v>
+      </c>
+      <c r="T12" s="5">
+        <v>1.81</v>
+      </c>
+      <c r="U12" s="5">
+        <v>758.5694446</v>
+      </c>
+      <c r="V12" s="5">
+        <v>8.5</v>
+      </c>
+      <c r="W12" s="5">
+        <v>45.5</v>
+      </c>
+      <c r="X12" s="6">
+        <v>1</v>
+      </c>
+      <c r="Y12" s="6">
+        <v>3</v>
+      </c>
+      <c r="Z12" s="6">
+        <v>2</v>
+      </c>
+      <c r="AA12" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB12" s="5">
+        <v>3.15</v>
+      </c>
+      <c r="AC12" s="5">
+        <v>357.99</v>
+      </c>
+      <c r="AD12" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AE12" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF12" s="5">
+        <v>459.45</v>
+      </c>
+      <c r="AG12" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH12" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI12" s="6">
+        <v>2</v>
+      </c>
+      <c r="AJ12" s="5">
+        <v>0.12</v>
+      </c>
+      <c r="AK12" s="5">
+        <v>410950</v>
+      </c>
+      <c r="AL12" s="5">
+        <v>59930</v>
+      </c>
+      <c r="AM12" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="AN12" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="A13" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B13" s="5">
+        <v>1200.1428000000001</v>
+      </c>
+      <c r="C13" s="5">
+        <v>10.647500000000001</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E13" s="7">
+        <v>4813</v>
+      </c>
+      <c r="F13" s="5">
+        <v>1.2549999999999999</v>
+      </c>
+      <c r="G13" s="5">
+        <v>172</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="I13" s="5">
+        <v>30.9</v>
+      </c>
+      <c r="J13" s="5">
+        <v>939.875</v>
+      </c>
+      <c r="K13" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="L13" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="M13" s="6">
+        <v>135</v>
+      </c>
+      <c r="N13" s="5">
+        <v>1</v>
+      </c>
+      <c r="O13" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="P13" s="6">
         <v>365</v>
       </c>
-      <c r="Q12" s="6">
-        <v>234</v>
-      </c>
-      <c r="R12" s="5">
-        <v>546.5</v>
-      </c>
-      <c r="S12" s="5">
-        <v>1950</v>
-      </c>
-      <c r="T12" s="5">
-        <v>1.96</v>
-      </c>
-      <c r="U12" s="5">
-        <v>861</v>
-      </c>
-      <c r="V12" s="5">
-        <v>2824</v>
-      </c>
-      <c r="W12" s="5">
-        <v>75</v>
-      </c>
-      <c r="X12" s="6">
-        <v>3</v>
-      </c>
-      <c r="Y12" s="6">
-        <v>4</v>
-      </c>
-      <c r="Z12" s="6">
-        <v>2</v>
-      </c>
-      <c r="AA12" s="5">
-        <v>20.5</v>
-      </c>
-      <c r="AB12" s="5">
-        <v>28</v>
-      </c>
-      <c r="AC12" s="5">
-        <v>665</v>
-      </c>
-      <c r="AD12" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AE12" s="6">
-        <v>2</v>
-      </c>
-      <c r="AF12" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AG12" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AH12" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="AI12" s="6">
-        <v>4</v>
-      </c>
-      <c r="AJ12" s="5">
-        <v>0.37</v>
-      </c>
-      <c r="AK12" s="5">
-        <v>416869</v>
-      </c>
-      <c r="AL12" s="5">
-        <v>154882</v>
-      </c>
-      <c r="AM12" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="AN12" s="3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:40">
-      <c r="A13" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="B13" s="5">
-        <v>1381</v>
-      </c>
-      <c r="C13" s="5">
-        <v>39.1</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E13" s="5">
-        <v>26427</v>
-      </c>
-      <c r="F13" s="5">
-        <v>1.74</v>
-      </c>
-      <c r="G13" s="5">
-        <v>262</v>
-      </c>
-      <c r="H13" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="I13" s="5">
-        <v>52.56</v>
-      </c>
-      <c r="J13" s="5">
-        <v>1598.7</v>
-      </c>
-      <c r="K13" s="6">
-        <v>1395</v>
-      </c>
-      <c r="L13" s="6">
-        <v>2008</v>
-      </c>
-      <c r="M13" s="6">
-        <v>164.5</v>
-      </c>
-      <c r="N13" s="5">
-        <v>1</v>
-      </c>
-      <c r="O13" s="5">
-        <v>1</v>
-      </c>
-      <c r="P13" s="6">
-        <v>730.5</v>
-      </c>
       <c r="Q13" s="6">
-        <v>168.33333329999999</v>
+        <v>165</v>
       </c>
       <c r="R13" s="5">
-        <v>187.1</v>
+        <v>29</v>
       </c>
       <c r="S13" s="5">
-        <v>450</v>
-      </c>
-      <c r="T13" s="5">
-        <v>3.44</v>
+        <v>500</v>
+      </c>
+      <c r="T13" s="5" t="s">
+        <v>42</v>
       </c>
       <c r="U13" s="5">
-        <v>1430.366667</v>
+        <v>774.875</v>
       </c>
       <c r="V13" s="5">
-        <v>120</v>
+        <v>1.5</v>
       </c>
       <c r="W13" s="5" t="s">
         <v>42</v>
       </c>
       <c r="X13" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y13" s="6">
         <v>3</v>
       </c>
       <c r="Z13" s="6">
-        <v>2</v>
-      </c>
-      <c r="AA13" s="5">
-        <v>66.5</v>
+        <v>1</v>
+      </c>
+      <c r="AA13" s="5" t="s">
+        <v>42</v>
       </c>
       <c r="AB13" s="5">
-        <v>91.2</v>
+        <v>2</v>
       </c>
       <c r="AC13" s="5">
-        <v>354.99</v>
+        <v>275</v>
       </c>
       <c r="AD13" s="5" t="s">
         <v>42</v>
@@ -2391,10 +2439,10 @@
         <v>42</v>
       </c>
       <c r="AH13" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI13" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AJ13" s="5" t="s">
         <v>42</v>
@@ -2409,10 +2457,10 @@
         <v>42</v>
       </c>
       <c r="AN13" s="3">
-        <v>11</v>
+        <v>40</v>
       </c>
     </row>
-    <row r="14" spans="1:40">
+    <row r="14" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
         <v>53</v>
       </c>
@@ -2534,48 +2582,48 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:40">
+    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
-        <v>54</v>
+        <v>83</v>
       </c>
       <c r="B15" s="5">
-        <v>7992.75</v>
+        <v>832.33299999999997</v>
       </c>
       <c r="C15" s="5">
-        <v>103.375</v>
+        <v>9.6850000000000005</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>42</v>
       </c>
       <c r="E15" s="5">
-        <v>68733</v>
+        <v>4443</v>
       </c>
       <c r="F15" s="5">
-        <v>1.865</v>
+        <v>1.145</v>
       </c>
       <c r="G15" s="5">
-        <v>742</v>
-      </c>
-      <c r="H15" s="5">
-        <v>32.700000000000003</v>
-      </c>
-      <c r="I15" s="5">
-        <v>49.05</v>
-      </c>
-      <c r="J15" s="5">
-        <v>1491.9375</v>
-      </c>
-      <c r="K15" s="6">
-        <v>2525.48</v>
-      </c>
-      <c r="L15" s="6">
-        <v>2525.48</v>
+        <v>73.7</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="J15" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="K15" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="L15" s="6" t="s">
+        <v>42</v>
       </c>
       <c r="M15" s="6">
-        <v>175</v>
+        <v>135</v>
       </c>
       <c r="N15" s="5">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="O15" s="5" t="s">
         <v>42</v>
@@ -2583,44 +2631,44 @@
       <c r="P15" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="Q15" s="6">
-        <v>365</v>
-      </c>
-      <c r="R15" s="5">
-        <v>498.58</v>
-      </c>
-      <c r="S15" s="5">
-        <v>2170</v>
-      </c>
-      <c r="T15" s="5">
-        <v>2.61</v>
-      </c>
-      <c r="U15" s="5">
-        <v>1126.9375</v>
+      <c r="Q15" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="R15" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="S15" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="T15" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="U15" s="5" t="s">
+        <v>42</v>
       </c>
       <c r="V15" s="5">
-        <v>410</v>
-      </c>
-      <c r="W15" s="5">
-        <v>64</v>
+        <v>1.5</v>
+      </c>
+      <c r="W15" s="5" t="s">
+        <v>42</v>
       </c>
       <c r="X15" s="6">
+        <v>2</v>
+      </c>
+      <c r="Y15" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z15" s="6">
+        <v>1</v>
+      </c>
+      <c r="AA15" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB15" s="5">
         <v>3</v>
       </c>
-      <c r="Y15" s="6">
-        <v>3</v>
-      </c>
-      <c r="Z15" s="6">
-        <v>2</v>
-      </c>
-      <c r="AA15" s="5">
-        <v>17</v>
-      </c>
-      <c r="AB15" s="5">
-        <v>16</v>
-      </c>
-      <c r="AC15" s="5">
-        <v>521.54999999999995</v>
+      <c r="AC15" s="5" t="s">
+        <v>42</v>
       </c>
       <c r="AD15" s="5" t="s">
         <v>42</v>
@@ -2637,8 +2685,8 @@
       <c r="AH15" s="6">
         <v>1</v>
       </c>
-      <c r="AI15" s="6" t="s">
-        <v>42</v>
+      <c r="AI15" s="6">
+        <v>2</v>
       </c>
       <c r="AJ15" s="5" t="s">
         <v>42</v>
@@ -2653,10 +2701,10 @@
         <v>42</v>
       </c>
       <c r="AN15" s="3">
-        <v>13</v>
+        <v>41</v>
       </c>
     </row>
-    <row r="16" spans="1:40">
+    <row r="16" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
         <v>55</v>
       </c>
@@ -2778,93 +2826,93 @@
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:40">
+    <row r="17" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="B17" s="5">
-        <v>7102.8333329999996</v>
+        <v>492.2</v>
       </c>
       <c r="C17" s="5">
-        <v>89.22</v>
+        <v>10.95</v>
       </c>
       <c r="D17" s="5">
-        <v>58</v>
+        <v>5.8</v>
       </c>
       <c r="E17" s="5">
-        <v>63482</v>
+        <v>6476</v>
       </c>
       <c r="F17" s="5">
-        <v>1.79</v>
+        <v>1.2549999999999999</v>
       </c>
       <c r="G17" s="5">
-        <v>834</v>
+        <v>47.9</v>
       </c>
       <c r="H17" s="5">
-        <v>36</v>
+        <v>17.899999999999999</v>
       </c>
       <c r="I17" s="5">
-        <v>50</v>
+        <v>15.733333330000001</v>
       </c>
       <c r="J17" s="5">
-        <v>1520.833333</v>
+        <v>478.55555550000003</v>
       </c>
       <c r="K17" s="6">
-        <v>1231</v>
+        <v>309.5</v>
       </c>
       <c r="L17" s="6">
-        <v>2007</v>
+        <v>395</v>
       </c>
       <c r="M17" s="6">
-        <v>165.66666670000001</v>
+        <v>153</v>
       </c>
       <c r="N17" s="5">
         <v>1</v>
       </c>
       <c r="O17" s="5">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="P17" s="6">
-        <v>404.5</v>
+        <v>206.66666670000001</v>
       </c>
       <c r="Q17" s="6">
-        <v>292.5</v>
+        <v>69.25</v>
       </c>
       <c r="R17" s="5">
-        <v>485.82499999999999</v>
+        <v>49.512500000000003</v>
       </c>
       <c r="S17" s="5">
-        <v>1435</v>
+        <v>167.5</v>
       </c>
       <c r="T17" s="5">
-        <v>2.46</v>
+        <v>0.7</v>
       </c>
       <c r="U17" s="5">
-        <v>1228.333333</v>
+        <v>409.30555550000003</v>
       </c>
       <c r="V17" s="5">
-        <v>400</v>
-      </c>
-      <c r="W17" s="5">
-        <v>63</v>
+        <v>45</v>
+      </c>
+      <c r="W17" s="5" t="s">
+        <v>42</v>
       </c>
       <c r="X17" s="6">
         <v>3</v>
       </c>
       <c r="Y17" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z17" s="6">
         <v>2</v>
       </c>
-      <c r="AA17" s="5">
-        <v>48</v>
+      <c r="AA17" s="5" t="s">
+        <v>42</v>
       </c>
       <c r="AB17" s="5">
-        <v>38.5</v>
+        <v>6.85</v>
       </c>
       <c r="AC17" s="5">
-        <v>555</v>
+        <v>280</v>
       </c>
       <c r="AD17" s="5" t="s">
         <v>42</v>
@@ -2872,198 +2920,198 @@
       <c r="AE17" s="6">
         <v>2</v>
       </c>
-      <c r="AF17" s="5">
-        <v>2239</v>
+      <c r="AF17" s="5" t="s">
+        <v>42</v>
       </c>
       <c r="AG17" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="AH17" s="6" t="s">
-        <v>42</v>
+      <c r="AH17" s="6">
+        <v>1</v>
       </c>
       <c r="AI17" s="6">
-        <v>3</v>
-      </c>
-      <c r="AJ17" s="5">
-        <v>0.27</v>
-      </c>
-      <c r="AK17" s="5">
-        <v>422149</v>
-      </c>
-      <c r="AL17" s="5">
-        <v>113783</v>
-      </c>
-      <c r="AM17" s="6">
-        <v>60</v>
+        <v>4</v>
+      </c>
+      <c r="AJ17" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AK17" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AL17" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AM17" s="6" t="s">
+        <v>42</v>
       </c>
       <c r="AN17" s="3">
-        <v>15</v>
+        <v>29</v>
       </c>
     </row>
-    <row r="18" spans="1:40">
+    <row r="18" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="B18" s="5">
-        <v>7854.8333329999996</v>
+        <v>288.12</v>
       </c>
       <c r="C18" s="5">
-        <v>76.75</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>42</v>
+        <v>7.6142857140000002</v>
+      </c>
+      <c r="D18" s="5">
+        <v>3.63</v>
       </c>
       <c r="E18" s="5">
-        <v>50906</v>
+        <v>4371</v>
       </c>
       <c r="F18" s="5">
-        <v>1.8049999999999999</v>
+        <v>1.17</v>
       </c>
       <c r="G18" s="5">
-        <v>455</v>
-      </c>
-      <c r="H18" s="5" t="s">
-        <v>42</v>
+        <v>52</v>
+      </c>
+      <c r="H18" s="5">
+        <v>16.75</v>
       </c>
       <c r="I18" s="5">
-        <v>45.45</v>
+        <v>18.25</v>
       </c>
       <c r="J18" s="5">
-        <v>1382.4375</v>
-      </c>
-      <c r="K18" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="L18" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="M18" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="N18" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="O18" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="P18" s="6" t="s">
-        <v>42</v>
+        <v>555.10416669999995</v>
+      </c>
+      <c r="K18" s="6">
+        <v>421</v>
+      </c>
+      <c r="L18" s="6">
+        <v>382</v>
+      </c>
+      <c r="M18" s="6">
+        <v>146</v>
+      </c>
+      <c r="N18" s="5">
+        <v>2.31</v>
+      </c>
+      <c r="O18" s="5">
+        <v>2</v>
+      </c>
+      <c r="P18" s="6">
+        <v>163</v>
       </c>
       <c r="Q18" s="6">
-        <v>656.2</v>
-      </c>
-      <c r="R18" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="S18" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="T18" s="5" t="s">
-        <v>42</v>
+        <v>70.400000000000006</v>
+      </c>
+      <c r="R18" s="5">
+        <v>27.932500000000001</v>
+      </c>
+      <c r="S18" s="5">
+        <v>107.785</v>
+      </c>
+      <c r="T18" s="5">
+        <v>0.85</v>
       </c>
       <c r="U18" s="5">
-        <v>726.23749999999995</v>
+        <v>484.70416669999997</v>
       </c>
       <c r="V18" s="5">
-        <v>71</v>
+        <v>6.5</v>
       </c>
       <c r="W18" s="5">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="X18" s="6">
         <v>3</v>
       </c>
-      <c r="Y18" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="Z18" s="6" t="s">
-        <v>42</v>
+      <c r="Y18" s="6">
+        <v>5</v>
+      </c>
+      <c r="Z18" s="6">
+        <v>2</v>
       </c>
       <c r="AA18" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="AB18" s="5" t="s">
+      <c r="AB18" s="5">
+        <v>8.5500000000000007</v>
+      </c>
+      <c r="AC18" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AD18" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AE18" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF18" s="5">
+        <v>152</v>
+      </c>
+      <c r="AG18" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH18" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI18" s="6">
+        <v>2</v>
+      </c>
+      <c r="AJ18" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AK18" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AL18" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AM18" s="6">
         <v>58</v>
       </c>
-      <c r="AC18" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AD18" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AE18" s="6">
-        <v>2</v>
-      </c>
-      <c r="AF18" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AG18" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AH18" s="6">
-        <v>1</v>
-      </c>
-      <c r="AI18" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="AJ18" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AK18" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AL18" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AM18" s="6" t="s">
-        <v>42</v>
-      </c>
       <c r="AN18" s="3">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
-    <row r="19" spans="1:40">
+    <row r="19" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="B19" s="5">
-        <v>8481.6666669999995</v>
+        <v>433.25</v>
       </c>
       <c r="C19" s="5">
-        <v>84.833333330000002</v>
+        <v>6.4333333330000002</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>42</v>
       </c>
       <c r="E19" s="5">
-        <v>48763</v>
+        <v>2938</v>
       </c>
       <c r="F19" s="5">
-        <v>1.635</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="G19" s="5">
-        <v>911</v>
+        <v>83.4</v>
       </c>
       <c r="H19" s="5">
-        <v>30</v>
-      </c>
-      <c r="I19" s="5">
-        <v>48</v>
-      </c>
-      <c r="J19" s="5">
-        <v>1460</v>
+        <v>15</v>
+      </c>
+      <c r="I19" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="J19" s="5" t="s">
+        <v>42</v>
       </c>
       <c r="K19" s="6">
-        <v>1460</v>
-      </c>
-      <c r="L19" s="6" t="s">
-        <v>42</v>
+        <v>365</v>
+      </c>
+      <c r="L19" s="6">
+        <v>365</v>
       </c>
       <c r="M19" s="6">
-        <v>190.5</v>
+        <v>70</v>
       </c>
       <c r="N19" s="5">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="O19" s="5">
         <v>1</v>
@@ -3072,10 +3120,10 @@
         <v>365</v>
       </c>
       <c r="Q19" s="6">
-        <v>330</v>
+        <v>45</v>
       </c>
       <c r="R19" s="5">
-        <v>428.25</v>
+        <v>14.09</v>
       </c>
       <c r="S19" s="5" t="s">
         <v>42</v>
@@ -3083,32 +3131,32 @@
       <c r="T19" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="U19" s="5">
-        <v>1130</v>
-      </c>
-      <c r="V19" s="5" t="s">
-        <v>42</v>
+      <c r="U19" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="V19" s="5">
+        <v>4.2</v>
       </c>
       <c r="W19" s="5" t="s">
         <v>42</v>
       </c>
       <c r="X19" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y19" s="6">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Z19" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA19" s="5">
-        <v>9.3000000000000007</v>
+        <v>1</v>
       </c>
       <c r="AB19" s="5">
-        <v>9.3000000000000007</v>
+        <v>1</v>
       </c>
       <c r="AC19" s="5">
-        <v>326.37</v>
+        <v>225</v>
       </c>
       <c r="AD19" s="5" t="s">
         <v>42</v>
@@ -3125,8 +3173,8 @@
       <c r="AH19" s="6">
         <v>1</v>
       </c>
-      <c r="AI19" s="6" t="s">
-        <v>42</v>
+      <c r="AI19" s="6">
+        <v>1</v>
       </c>
       <c r="AJ19" s="5" t="s">
         <v>42</v>
@@ -3141,96 +3189,96 @@
         <v>42</v>
       </c>
       <c r="AN19" s="3">
-        <v>17</v>
+        <v>38</v>
       </c>
     </row>
-    <row r="20" spans="1:40">
+    <row r="20" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
-        <v>60</v>
+        <v>81</v>
       </c>
       <c r="B20" s="5">
-        <v>99648.4</v>
+        <v>214</v>
       </c>
       <c r="C20" s="5">
-        <v>477.44</v>
-      </c>
-      <c r="D20" s="5">
-        <v>227</v>
+        <v>3.0133333329999998</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>42</v>
       </c>
       <c r="E20" s="5">
-        <v>341444</v>
+        <v>1221</v>
       </c>
       <c r="F20" s="5">
-        <v>2.2599999999999998</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="G20" s="5">
-        <v>3608</v>
+        <v>24.6</v>
       </c>
       <c r="H20" s="5">
-        <v>50</v>
+        <v>19.25</v>
       </c>
       <c r="I20" s="5">
-        <v>103.5</v>
+        <v>14.33333333</v>
       </c>
       <c r="J20" s="5">
-        <v>3148.125</v>
+        <v>435.97222210000001</v>
       </c>
       <c r="K20" s="6">
-        <v>2829</v>
+        <v>365</v>
       </c>
       <c r="L20" s="6">
-        <v>4015</v>
+        <v>730</v>
       </c>
       <c r="M20" s="6">
-        <v>264.5</v>
+        <v>61.666666669999998</v>
       </c>
       <c r="N20" s="5">
-        <v>1</v>
+        <v>2.25</v>
       </c>
       <c r="O20" s="5">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="P20" s="6">
-        <v>1403.5</v>
+        <v>365</v>
       </c>
       <c r="Q20" s="6">
-        <v>1004</v>
+        <v>61.5</v>
       </c>
       <c r="R20" s="5">
-        <v>1979.25</v>
-      </c>
-      <c r="S20" s="5">
-        <v>12595</v>
+        <v>19</v>
+      </c>
+      <c r="S20" s="5" t="s">
+        <v>42</v>
       </c>
       <c r="T20" s="5">
-        <v>6.58</v>
+        <v>0.86</v>
       </c>
       <c r="U20" s="5">
-        <v>2144.125</v>
+        <v>374.47222210000001</v>
       </c>
       <c r="V20" s="5">
-        <v>1800</v>
-      </c>
-      <c r="W20" s="5">
-        <v>67</v>
+        <v>4</v>
+      </c>
+      <c r="W20" s="5" t="s">
+        <v>42</v>
       </c>
       <c r="X20" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y20" s="6">
-        <v>3</v>
-      </c>
-      <c r="Z20" s="6" t="s">
-        <v>42</v>
+        <v>5</v>
+      </c>
+      <c r="Z20" s="6">
+        <v>2</v>
       </c>
       <c r="AA20" s="5">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="AB20" s="5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AC20" s="5">
-        <v>1594.44</v>
+        <v>225</v>
       </c>
       <c r="AD20" s="5" t="s">
         <v>42</v>
@@ -3238,35 +3286,35 @@
       <c r="AE20" s="6">
         <v>2</v>
       </c>
-      <c r="AF20" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AG20" s="5">
-        <v>5248.98</v>
+      <c r="AF20" s="5">
+        <v>148.1</v>
+      </c>
+      <c r="AG20" s="5" t="s">
+        <v>42</v>
       </c>
       <c r="AH20" s="6">
         <v>1</v>
       </c>
       <c r="AI20" s="6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AJ20" s="5">
-        <v>0.95</v>
+        <v>0.59</v>
       </c>
       <c r="AK20" s="5">
-        <v>144544</v>
+        <v>186209</v>
       </c>
       <c r="AL20" s="5">
-        <v>138038</v>
+        <v>109648</v>
       </c>
       <c r="AM20" s="6" t="s">
         <v>42</v>
       </c>
       <c r="AN20" s="3">
-        <v>18</v>
+        <v>39</v>
       </c>
     </row>
-    <row r="21" spans="1:40">
+    <row r="21" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
         <v>61</v>
       </c>
@@ -3388,78 +3436,78 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:40">
+    <row r="22" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="B22" s="5">
-        <v>41057.090909999999</v>
+        <v>2640.2849999999999</v>
       </c>
       <c r="C22" s="5">
-        <v>392.06</v>
-      </c>
-      <c r="D22" s="5">
-        <v>128</v>
+        <v>44.887500000000003</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>42</v>
       </c>
       <c r="E22" s="5">
-        <v>291592</v>
+        <v>22127</v>
       </c>
       <c r="F22" s="5">
-        <v>2.4550000000000001</v>
+        <v>1.25</v>
       </c>
       <c r="G22" s="5">
-        <v>1899</v>
+        <v>392</v>
       </c>
       <c r="H22" s="5">
-        <v>59.4</v>
+        <v>24.25</v>
       </c>
       <c r="I22" s="5">
-        <v>164.8</v>
+        <v>35.5</v>
       </c>
       <c r="J22" s="5">
-        <v>5012.6666670000004</v>
+        <v>1079.791667</v>
       </c>
       <c r="K22" s="6">
-        <v>3376</v>
-      </c>
-      <c r="L22" s="6">
-        <v>2920</v>
+        <v>882</v>
+      </c>
+      <c r="L22" s="6" t="s">
+        <v>42</v>
       </c>
       <c r="M22" s="6">
-        <v>234</v>
+        <v>164.5</v>
       </c>
       <c r="N22" s="5">
         <v>1</v>
       </c>
       <c r="O22" s="5">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="P22" s="6">
-        <v>1320</v>
+        <v>756</v>
       </c>
       <c r="Q22" s="6">
-        <v>1579.5</v>
+        <v>244</v>
       </c>
       <c r="R22" s="5">
-        <v>1736.25</v>
+        <v>119.33333330000001</v>
       </c>
       <c r="S22" s="5">
-        <v>8500</v>
+        <v>1535</v>
       </c>
       <c r="T22" s="5">
-        <v>8.3000000000000007</v>
+        <v>2.04</v>
       </c>
       <c r="U22" s="5">
-        <v>3433.166667</v>
+        <v>835.79166669999995</v>
       </c>
       <c r="V22" s="5">
-        <v>1085</v>
+        <v>11</v>
       </c>
       <c r="W22" s="5">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="X22" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y22" s="6">
         <v>6</v>
@@ -3468,22 +3516,22 @@
         <v>2</v>
       </c>
       <c r="AA22" s="5">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="AB22" s="5">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="AC22" s="5">
-        <v>796.09</v>
-      </c>
-      <c r="AD22" s="5">
-        <v>0</v>
+        <v>400</v>
+      </c>
+      <c r="AD22" s="5" t="s">
+        <v>42</v>
       </c>
       <c r="AE22" s="6">
         <v>2</v>
       </c>
       <c r="AF22" s="5">
-        <v>9000</v>
+        <v>1393.9</v>
       </c>
       <c r="AG22" s="5" t="s">
         <v>42</v>
@@ -3491,26 +3539,26 @@
       <c r="AH22" s="6">
         <v>2</v>
       </c>
-      <c r="AI22" s="6">
-        <v>3</v>
-      </c>
-      <c r="AJ22" s="5">
-        <v>0.59</v>
-      </c>
-      <c r="AK22" s="5">
-        <v>208930</v>
-      </c>
-      <c r="AL22" s="5">
-        <v>123027</v>
+      <c r="AI22" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="AJ22" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AK22" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AL22" s="5" t="s">
+        <v>42</v>
       </c>
       <c r="AM22" s="6" t="s">
         <v>42</v>
       </c>
       <c r="AN22" s="3">
-        <v>20</v>
+        <v>44</v>
       </c>
     </row>
-    <row r="23" spans="1:40">
+    <row r="23" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
         <v>63</v>
       </c>
@@ -3632,75 +3680,75 @@
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:40">
+    <row r="24" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="B24" s="5">
-        <v>5724.8571430000002</v>
+        <v>7421.4</v>
       </c>
       <c r="C24" s="5">
-        <v>101.52</v>
-      </c>
-      <c r="D24" s="5">
-        <v>65</v>
+        <v>105.65</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>42</v>
       </c>
       <c r="E24" s="5">
-        <v>65800</v>
+        <v>77141</v>
       </c>
       <c r="F24" s="5">
-        <v>1.855</v>
+        <v>1.91</v>
       </c>
       <c r="G24" s="5">
-        <v>555</v>
+        <v>561</v>
       </c>
       <c r="H24" s="5">
-        <v>44</v>
+        <v>21.6</v>
       </c>
       <c r="I24" s="5">
-        <v>101.19333330000001</v>
+        <v>36</v>
       </c>
       <c r="J24" s="5">
-        <v>3077.9638880000002</v>
+        <v>1095</v>
       </c>
       <c r="K24" s="6">
-        <v>2555</v>
+        <v>1246.07</v>
       </c>
       <c r="L24" s="6">
-        <v>1825</v>
+        <v>1246.07</v>
       </c>
       <c r="M24" s="6">
-        <v>212</v>
+        <v>167</v>
       </c>
       <c r="N24" s="5">
         <v>1</v>
       </c>
-      <c r="O24" s="5">
-        <v>0.5</v>
+      <c r="O24" s="5" t="s">
+        <v>42</v>
       </c>
       <c r="P24" s="6">
-        <v>997.5</v>
+        <v>365</v>
       </c>
       <c r="Q24" s="6">
-        <v>626</v>
+        <v>234</v>
       </c>
       <c r="R24" s="5">
-        <v>378.55</v>
+        <v>546.5</v>
       </c>
       <c r="S24" s="5">
-        <v>1070</v>
+        <v>1950</v>
       </c>
       <c r="T24" s="5">
-        <v>6.73</v>
+        <v>1.96</v>
       </c>
       <c r="U24" s="5">
-        <v>2451.9638880000002</v>
+        <v>861</v>
       </c>
       <c r="V24" s="5">
-        <v>57</v>
+        <v>2824</v>
       </c>
       <c r="W24" s="5">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="X24" s="6">
         <v>3</v>
@@ -3711,14 +3759,14 @@
       <c r="Z24" s="6">
         <v>2</v>
       </c>
-      <c r="AA24" s="5" t="s">
-        <v>42</v>
+      <c r="AA24" s="5">
+        <v>20.5</v>
       </c>
       <c r="AB24" s="5">
-        <v>3.2</v>
+        <v>28</v>
       </c>
       <c r="AC24" s="5">
-        <v>545</v>
+        <v>665</v>
       </c>
       <c r="AD24" s="5" t="s">
         <v>42</v>
@@ -3736,25 +3784,25 @@
         <v>42</v>
       </c>
       <c r="AI24" s="6">
-        <v>2</v>
-      </c>
-      <c r="AJ24" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AK24" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AL24" s="5" t="s">
-        <v>42</v>
+        <v>4</v>
+      </c>
+      <c r="AJ24" s="5">
+        <v>0.37</v>
+      </c>
+      <c r="AK24" s="5">
+        <v>416869</v>
+      </c>
+      <c r="AL24" s="5">
+        <v>154882</v>
       </c>
       <c r="AM24" s="6" t="s">
         <v>42</v>
       </c>
       <c r="AN24" s="3">
-        <v>22</v>
+        <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:40">
+    <row r="25" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
         <v>65</v>
       </c>
@@ -3876,7 +3924,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:40">
+    <row r="26" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
         <v>66</v>
       </c>
@@ -3998,7 +4046,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:40">
+    <row r="27" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A27" s="4" t="s">
         <v>67</v>
       </c>
@@ -4120,78 +4168,78 @@
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:40">
+    <row r="28" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A28" s="4" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="B28" s="5">
-        <v>5959</v>
+        <v>1933.8</v>
       </c>
       <c r="C28" s="5">
-        <v>95.575000000000003</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>42</v>
+        <v>28.1</v>
+      </c>
+      <c r="D28" s="5">
+        <v>10.69</v>
       </c>
       <c r="E28" s="5">
-        <v>65873</v>
+        <v>12207</v>
       </c>
       <c r="F28" s="5">
-        <v>1.97</v>
+        <v>1.46</v>
       </c>
       <c r="G28" s="5">
-        <v>1090</v>
+        <v>194</v>
       </c>
       <c r="H28" s="5">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I28" s="5">
-        <v>75.5</v>
+        <v>29.875</v>
       </c>
       <c r="J28" s="5">
-        <v>2296.458333</v>
+        <v>908.69791669999995</v>
       </c>
       <c r="K28" s="6">
-        <v>2555</v>
+        <v>548</v>
       </c>
       <c r="L28" s="6">
-        <v>1520</v>
+        <v>548</v>
       </c>
       <c r="M28" s="6">
-        <v>224</v>
+        <v>120</v>
       </c>
       <c r="N28" s="5">
         <v>1</v>
       </c>
-      <c r="O28" s="5">
-        <v>0.5</v>
+      <c r="O28" s="5" t="s">
+        <v>42</v>
       </c>
       <c r="P28" s="6">
-        <v>288</v>
+        <v>730</v>
       </c>
       <c r="Q28" s="6">
-        <v>391.33333329999999</v>
+        <v>159</v>
       </c>
       <c r="R28" s="5">
-        <v>393</v>
-      </c>
-      <c r="S28" s="5" t="s">
-        <v>42</v>
+        <v>75.7</v>
+      </c>
+      <c r="S28" s="5">
+        <v>1350</v>
       </c>
       <c r="T28" s="5">
-        <v>3.53</v>
+        <v>1.46</v>
       </c>
       <c r="U28" s="5">
-        <v>1905.125</v>
+        <v>749.69791669999995</v>
       </c>
       <c r="V28" s="5">
-        <v>400</v>
-      </c>
-      <c r="W28" s="5">
-        <v>79</v>
+        <v>8.75</v>
+      </c>
+      <c r="W28" s="5" t="s">
+        <v>42</v>
       </c>
       <c r="X28" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y28" s="6">
         <v>4</v>
@@ -4199,14 +4247,14 @@
       <c r="Z28" s="6">
         <v>2</v>
       </c>
-      <c r="AA28" s="5" t="s">
-        <v>42</v>
+      <c r="AA28" s="5">
+        <v>9.25</v>
       </c>
       <c r="AB28" s="5">
-        <v>33</v>
+        <v>9.15</v>
       </c>
       <c r="AC28" s="5">
-        <v>536.39</v>
+        <v>469.62</v>
       </c>
       <c r="AD28" s="5" t="s">
         <v>42</v>
@@ -4239,10 +4287,10 @@
         <v>42</v>
       </c>
       <c r="AN28" s="3">
-        <v>26</v>
+        <v>45</v>
       </c>
     </row>
-    <row r="29" spans="1:40">
+    <row r="29" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A29" s="4" t="s">
         <v>69</v>
       </c>
@@ -4364,204 +4412,204 @@
         <v>27</v>
       </c>
     </row>
-    <row r="30" spans="1:40">
+    <row r="30" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
-        <v>70</v>
+        <v>97</v>
       </c>
       <c r="B30" s="5">
-        <v>783.6</v>
+        <v>71.5</v>
       </c>
       <c r="C30" s="5">
-        <v>17.399999999999999</v>
+        <v>3.3450000000000002</v>
       </c>
       <c r="D30" s="5">
-        <v>10.1</v>
+        <v>1.1990000000000001</v>
       </c>
       <c r="E30" s="5">
-        <v>9950</v>
+        <v>1568</v>
       </c>
       <c r="F30" s="5">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="G30" s="5">
-        <v>105</v>
+        <v>30.4</v>
       </c>
       <c r="H30" s="5">
-        <v>25.25</v>
+        <v>14</v>
       </c>
       <c r="I30" s="5">
-        <v>28.56666667</v>
+        <v>21.4</v>
       </c>
       <c r="J30" s="5">
-        <v>868.90277790000005</v>
+        <v>650.91666669999995</v>
       </c>
       <c r="K30" s="6">
-        <v>821</v>
+        <v>240</v>
       </c>
       <c r="L30" s="6">
-        <v>730</v>
+        <v>274</v>
       </c>
       <c r="M30" s="6">
-        <v>137.5</v>
+        <v>110.33333330000001</v>
       </c>
       <c r="N30" s="5">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="O30" s="5">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="P30" s="6">
-        <v>269</v>
+        <v>330</v>
       </c>
       <c r="Q30" s="6">
-        <v>110.33333330000001</v>
+        <v>45</v>
       </c>
       <c r="R30" s="5">
-        <v>91.25</v>
-      </c>
-      <c r="S30" s="5">
-        <v>360</v>
-      </c>
-      <c r="T30" s="5">
-        <v>1.81</v>
+        <v>8.4666666670000001</v>
+      </c>
+      <c r="S30" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="T30" s="5" t="s">
+        <v>42</v>
       </c>
       <c r="U30" s="5">
-        <v>758.5694446</v>
+        <v>605.91666669999995</v>
       </c>
       <c r="V30" s="5">
-        <v>8.5</v>
-      </c>
-      <c r="W30" s="5">
-        <v>45.5</v>
+        <v>1</v>
+      </c>
+      <c r="W30" s="5" t="s">
+        <v>42</v>
       </c>
       <c r="X30" s="6">
         <v>1</v>
       </c>
       <c r="Y30" s="6">
+        <v>4</v>
+      </c>
+      <c r="Z30" s="6">
+        <v>2</v>
+      </c>
+      <c r="AA30" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB30" s="5">
+        <v>5.5</v>
+      </c>
+      <c r="AC30" s="5">
+        <v>120</v>
+      </c>
+      <c r="AD30" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AE30" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF30" s="5">
+        <v>59.4</v>
+      </c>
+      <c r="AG30" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH30" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="AI30" s="6">
+        <v>4</v>
+      </c>
+      <c r="AJ30" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AK30" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AL30" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AM30" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="AN30" s="3">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="31" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="A31" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B31" s="5">
+        <v>178.7</v>
+      </c>
+      <c r="C31" s="5">
+        <v>4.8</v>
+      </c>
+      <c r="D31" s="5">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="E31" s="5">
+        <v>2139</v>
+      </c>
+      <c r="F31" s="5">
+        <v>1.17</v>
+      </c>
+      <c r="G31" s="5">
+        <v>40.200000000000003</v>
+      </c>
+      <c r="H31" s="5">
+        <v>17</v>
+      </c>
+      <c r="I31" s="5">
+        <v>11.4</v>
+      </c>
+      <c r="J31" s="5">
+        <v>346.75</v>
+      </c>
+      <c r="K31" s="6">
+        <v>240</v>
+      </c>
+      <c r="L31" s="6">
+        <v>300</v>
+      </c>
+      <c r="M31" s="6">
+        <v>130.66666670000001</v>
+      </c>
+      <c r="N31" s="5">
+        <v>1.55</v>
+      </c>
+      <c r="O31" s="5">
+        <v>2</v>
+      </c>
+      <c r="P31" s="6">
+        <v>242.5</v>
+      </c>
+      <c r="Q31" s="6">
+        <v>87.333333330000002</v>
+      </c>
+      <c r="R31" s="5">
+        <v>15.55</v>
+      </c>
+      <c r="S31" s="5">
+        <v>125</v>
+      </c>
+      <c r="T31" s="5">
+        <v>0.74</v>
+      </c>
+      <c r="U31" s="5">
+        <v>259.41666670000001</v>
+      </c>
+      <c r="V31" s="5">
+        <v>11</v>
+      </c>
+      <c r="W31" s="5">
+        <v>0</v>
+      </c>
+      <c r="X31" s="6">
+        <v>1</v>
+      </c>
+      <c r="Y31" s="6">
         <v>3</v>
       </c>
-      <c r="Z30" s="6">
-        <v>2</v>
-      </c>
-      <c r="AA30" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AB30" s="5">
-        <v>3.15</v>
-      </c>
-      <c r="AC30" s="5">
-        <v>357.99</v>
-      </c>
-      <c r="AD30" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AE30" s="6">
-        <v>2</v>
-      </c>
-      <c r="AF30" s="5">
-        <v>459.45</v>
-      </c>
-      <c r="AG30" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AH30" s="6">
-        <v>1</v>
-      </c>
-      <c r="AI30" s="6">
-        <v>2</v>
-      </c>
-      <c r="AJ30" s="5">
-        <v>0.12</v>
-      </c>
-      <c r="AK30" s="5">
-        <v>410950</v>
-      </c>
-      <c r="AL30" s="5">
-        <v>59930</v>
-      </c>
-      <c r="AM30" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="AN30" s="3">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="31" spans="1:40">
-      <c r="A31" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="B31" s="5">
-        <v>492.2</v>
-      </c>
-      <c r="C31" s="5">
-        <v>10.95</v>
-      </c>
-      <c r="D31" s="5">
-        <v>5.8</v>
-      </c>
-      <c r="E31" s="5">
-        <v>6476</v>
-      </c>
-      <c r="F31" s="5">
-        <v>1.2549999999999999</v>
-      </c>
-      <c r="G31" s="5">
-        <v>47.9</v>
-      </c>
-      <c r="H31" s="5">
-        <v>17.899999999999999</v>
-      </c>
-      <c r="I31" s="5">
-        <v>15.733333330000001</v>
-      </c>
-      <c r="J31" s="5">
-        <v>478.55555550000003</v>
-      </c>
-      <c r="K31" s="6">
-        <v>309.5</v>
-      </c>
-      <c r="L31" s="6">
-        <v>395</v>
-      </c>
-      <c r="M31" s="6">
-        <v>153</v>
-      </c>
-      <c r="N31" s="5">
-        <v>1</v>
-      </c>
-      <c r="O31" s="5">
-        <v>1.2</v>
-      </c>
-      <c r="P31" s="6">
-        <v>206.66666670000001</v>
-      </c>
-      <c r="Q31" s="6">
-        <v>69.25</v>
-      </c>
-      <c r="R31" s="5">
-        <v>49.512500000000003</v>
-      </c>
-      <c r="S31" s="5">
-        <v>167.5</v>
-      </c>
-      <c r="T31" s="5">
-        <v>0.7</v>
-      </c>
-      <c r="U31" s="5">
-        <v>409.30555550000003</v>
-      </c>
-      <c r="V31" s="5">
-        <v>45</v>
-      </c>
-      <c r="W31" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="X31" s="6">
-        <v>3</v>
-      </c>
-      <c r="Y31" s="6">
-        <v>2</v>
-      </c>
       <c r="Z31" s="6">
         <v>2</v>
       </c>
@@ -4569,10 +4617,10 @@
         <v>42</v>
       </c>
       <c r="AB31" s="5">
-        <v>6.85</v>
+        <v>3.5</v>
       </c>
       <c r="AC31" s="5">
-        <v>280</v>
+        <v>160</v>
       </c>
       <c r="AD31" s="5" t="s">
         <v>42</v>
@@ -4580,121 +4628,121 @@
       <c r="AE31" s="6">
         <v>2</v>
       </c>
-      <c r="AF31" s="5" t="s">
-        <v>42</v>
+      <c r="AF31" s="5">
+        <v>180.22499999999999</v>
       </c>
       <c r="AG31" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="AH31" s="6">
-        <v>1</v>
+      <c r="AH31" s="6" t="s">
+        <v>42</v>
       </c>
       <c r="AI31" s="6">
         <v>4</v>
       </c>
-      <c r="AJ31" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AK31" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AL31" s="5" t="s">
-        <v>42</v>
+      <c r="AJ31" s="5">
+        <v>0.45</v>
+      </c>
+      <c r="AK31" s="5">
+        <v>338844</v>
+      </c>
+      <c r="AL31" s="5">
+        <v>151356</v>
       </c>
       <c r="AM31" s="6" t="s">
         <v>42</v>
       </c>
       <c r="AN31" s="3">
-        <v>29</v>
+        <v>53</v>
       </c>
     </row>
-    <row r="32" spans="1:40">
+    <row r="32" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A32" s="4" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="B32" s="5">
-        <v>288.12</v>
+        <v>99648.4</v>
       </c>
       <c r="C32" s="5">
-        <v>7.6142857140000002</v>
+        <v>477.44</v>
       </c>
       <c r="D32" s="5">
-        <v>3.63</v>
-      </c>
-      <c r="E32" s="5">
-        <v>4371</v>
+        <v>227</v>
+      </c>
+      <c r="E32" s="8">
+        <v>341444</v>
       </c>
       <c r="F32" s="5">
-        <v>1.17</v>
+        <v>2.2599999999999998</v>
       </c>
       <c r="G32" s="5">
-        <v>52</v>
+        <v>3608</v>
       </c>
       <c r="H32" s="5">
-        <v>16.75</v>
+        <v>50</v>
       </c>
       <c r="I32" s="5">
-        <v>18.25</v>
+        <v>103.5</v>
       </c>
       <c r="J32" s="5">
-        <v>555.10416669999995</v>
+        <v>3148.125</v>
       </c>
       <c r="K32" s="6">
-        <v>421</v>
+        <v>2829</v>
       </c>
       <c r="L32" s="6">
-        <v>382</v>
+        <v>4015</v>
       </c>
       <c r="M32" s="6">
-        <v>146</v>
+        <v>264.5</v>
       </c>
       <c r="N32" s="5">
-        <v>2.31</v>
+        <v>1</v>
       </c>
       <c r="O32" s="5">
-        <v>2</v>
+        <v>0.3</v>
       </c>
       <c r="P32" s="6">
-        <v>163</v>
+        <v>1403.5</v>
       </c>
       <c r="Q32" s="6">
-        <v>70.400000000000006</v>
+        <v>1004</v>
       </c>
       <c r="R32" s="5">
-        <v>27.932500000000001</v>
+        <v>1979.25</v>
       </c>
       <c r="S32" s="5">
-        <v>107.785</v>
+        <v>12595</v>
       </c>
       <c r="T32" s="5">
-        <v>0.85</v>
+        <v>6.58</v>
       </c>
       <c r="U32" s="5">
-        <v>484.70416669999997</v>
+        <v>2144.125</v>
       </c>
       <c r="V32" s="5">
-        <v>6.5</v>
+        <v>1800</v>
       </c>
       <c r="W32" s="5">
-        <v>22</v>
+        <v>67</v>
       </c>
       <c r="X32" s="6">
         <v>3</v>
       </c>
       <c r="Y32" s="6">
-        <v>5</v>
-      </c>
-      <c r="Z32" s="6">
-        <v>2</v>
-      </c>
-      <c r="AA32" s="5" t="s">
-        <v>42</v>
+        <v>3</v>
+      </c>
+      <c r="Z32" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA32" s="5">
+        <v>10</v>
       </c>
       <c r="AB32" s="5">
-        <v>8.5500000000000007</v>
-      </c>
-      <c r="AC32" s="5" t="s">
-        <v>42</v>
+        <v>6</v>
+      </c>
+      <c r="AC32" s="5">
+        <v>1594.44</v>
       </c>
       <c r="AD32" s="5" t="s">
         <v>42</v>
@@ -4702,103 +4750,103 @@
       <c r="AE32" s="6">
         <v>2</v>
       </c>
-      <c r="AF32" s="5">
-        <v>152</v>
-      </c>
-      <c r="AG32" s="5" t="s">
-        <v>42</v>
+      <c r="AF32" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AG32" s="5">
+        <v>5248.98</v>
       </c>
       <c r="AH32" s="6">
         <v>1</v>
       </c>
       <c r="AI32" s="6">
-        <v>2</v>
-      </c>
-      <c r="AJ32" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AK32" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AL32" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AM32" s="6">
-        <v>58</v>
+        <v>4</v>
+      </c>
+      <c r="AJ32" s="5">
+        <v>0.95</v>
+      </c>
+      <c r="AK32" s="5">
+        <v>144544</v>
+      </c>
+      <c r="AL32" s="5">
+        <v>138038</v>
+      </c>
+      <c r="AM32" s="6" t="s">
+        <v>42</v>
       </c>
       <c r="AN32" s="3">
-        <v>30</v>
+        <v>18</v>
       </c>
     </row>
-    <row r="33" spans="1:40">
+    <row r="33" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A33" s="4" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="B33" s="5">
-        <v>439.2</v>
+        <v>5724.8571430000002</v>
       </c>
       <c r="C33" s="5">
-        <v>10.5</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E33" s="5">
-        <v>5883</v>
+        <v>101.52</v>
+      </c>
+      <c r="D33" s="5">
+        <v>65</v>
+      </c>
+      <c r="E33" s="8">
+        <v>65800</v>
       </c>
       <c r="F33" s="5">
-        <v>1.1950000000000001</v>
+        <v>1.855</v>
       </c>
       <c r="G33" s="5">
-        <v>251</v>
+        <v>555</v>
       </c>
       <c r="H33" s="5">
-        <v>13.3</v>
+        <v>44</v>
       </c>
       <c r="I33" s="5">
-        <v>24</v>
+        <v>101.19333330000001</v>
       </c>
       <c r="J33" s="5">
-        <v>730</v>
+        <v>3077.9638880000002</v>
       </c>
       <c r="K33" s="6">
-        <v>608</v>
-      </c>
-      <c r="L33" s="6" t="s">
-        <v>42</v>
+        <v>2555</v>
+      </c>
+      <c r="L33" s="6">
+        <v>1825</v>
       </c>
       <c r="M33" s="6">
-        <v>140.5</v>
+        <v>212</v>
       </c>
       <c r="N33" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O33" s="5">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="P33" s="6">
-        <v>240</v>
+        <v>997.5</v>
       </c>
       <c r="Q33" s="6">
-        <v>70.5</v>
+        <v>626</v>
       </c>
       <c r="R33" s="5">
-        <v>38</v>
-      </c>
-      <c r="S33" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="T33" s="5" t="s">
-        <v>42</v>
+        <v>378.55</v>
+      </c>
+      <c r="S33" s="5">
+        <v>1070</v>
+      </c>
+      <c r="T33" s="5">
+        <v>6.73</v>
       </c>
       <c r="U33" s="5">
-        <v>659.5</v>
+        <v>2451.9638880000002</v>
       </c>
       <c r="V33" s="5">
-        <v>9</v>
+        <v>57</v>
       </c>
       <c r="W33" s="5">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="X33" s="6">
         <v>3</v>
@@ -4813,10 +4861,10 @@
         <v>42</v>
       </c>
       <c r="AB33" s="5">
-        <v>5.55</v>
+        <v>3.2</v>
       </c>
       <c r="AC33" s="5">
-        <v>264.20999999999998</v>
+        <v>545</v>
       </c>
       <c r="AD33" s="5" t="s">
         <v>42</v>
@@ -4833,8 +4881,8 @@
       <c r="AH33" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="AI33" s="6" t="s">
-        <v>42</v>
+      <c r="AI33" s="6">
+        <v>2</v>
       </c>
       <c r="AJ33" s="5" t="s">
         <v>42</v>
@@ -4849,78 +4897,78 @@
         <v>42</v>
       </c>
       <c r="AN33" s="3">
-        <v>31</v>
+        <v>22</v>
       </c>
     </row>
-    <row r="34" spans="1:40">
+    <row r="34" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A34" s="4" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="B34" s="5">
-        <v>368.83333329999999</v>
+        <v>7410.8333000000002</v>
       </c>
       <c r="C34" s="5">
-        <v>9.8000000000000007</v>
+        <v>37.35</v>
       </c>
       <c r="D34" s="5" t="s">
         <v>42</v>
       </c>
       <c r="E34" s="5">
-        <v>5894</v>
+        <v>20114</v>
       </c>
       <c r="F34" s="5">
-        <v>1.1950000000000001</v>
-      </c>
-      <c r="G34" s="5" t="s">
-        <v>42</v>
+        <v>1.4550000000000001</v>
+      </c>
+      <c r="G34" s="5">
+        <v>330</v>
       </c>
       <c r="H34" s="5">
-        <v>23.08</v>
+        <v>34.5</v>
       </c>
       <c r="I34" s="5">
-        <v>22.8</v>
+        <v>84</v>
       </c>
       <c r="J34" s="5">
-        <v>693.5</v>
+        <v>2555</v>
       </c>
       <c r="K34" s="6">
-        <v>548</v>
+        <v>2008</v>
       </c>
       <c r="L34" s="6">
-        <v>550</v>
+        <v>2008</v>
       </c>
       <c r="M34" s="6">
-        <v>161.5</v>
+        <v>159.5</v>
       </c>
       <c r="N34" s="5">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="O34" s="5">
-        <v>1</v>
+        <v>0.42</v>
       </c>
       <c r="P34" s="6">
-        <v>262</v>
+        <v>906</v>
       </c>
       <c r="Q34" s="6">
-        <v>52</v>
+        <v>364.33333329999999</v>
       </c>
       <c r="R34" s="5">
-        <v>41.28</v>
-      </c>
-      <c r="S34" s="5">
-        <v>105</v>
+        <v>300</v>
+      </c>
+      <c r="S34" s="5" t="s">
+        <v>42</v>
       </c>
       <c r="T34" s="5" t="s">
         <v>42</v>
       </c>
       <c r="U34" s="5">
-        <v>641.5</v>
+        <v>2190.666667</v>
       </c>
       <c r="V34" s="5">
-        <v>32</v>
-      </c>
-      <c r="W34" s="5" t="s">
-        <v>42</v>
+        <v>18</v>
+      </c>
+      <c r="W34" s="5">
+        <v>43</v>
       </c>
       <c r="X34" s="6">
         <v>3</v>
@@ -4929,16 +4977,16 @@
         <v>4</v>
       </c>
       <c r="Z34" s="6">
-        <v>2</v>
-      </c>
-      <c r="AA34" s="5" t="s">
-        <v>42</v>
+        <v>1</v>
+      </c>
+      <c r="AA34" s="5">
+        <v>3.5</v>
       </c>
       <c r="AB34" s="5">
-        <v>7.05</v>
+        <v>3.1</v>
       </c>
       <c r="AC34" s="5">
-        <v>239.99</v>
+        <v>734.99</v>
       </c>
       <c r="AD34" s="5" t="s">
         <v>42</v>
@@ -4955,26 +5003,26 @@
       <c r="AH34" s="6">
         <v>1</v>
       </c>
-      <c r="AI34" s="6">
-        <v>2</v>
-      </c>
-      <c r="AJ34" s="5">
-        <v>0.3</v>
-      </c>
-      <c r="AK34" s="5">
-        <v>328541</v>
-      </c>
-      <c r="AL34" s="5">
-        <v>102329</v>
+      <c r="AI34" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="AJ34" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AK34" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AL34" s="5" t="s">
+        <v>42</v>
       </c>
       <c r="AM34" s="6" t="s">
         <v>42</v>
       </c>
       <c r="AN34" s="3">
-        <v>32</v>
+        <v>43</v>
       </c>
     </row>
-    <row r="35" spans="1:40">
+    <row r="35" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A35" s="4" t="s">
         <v>75</v>
       </c>
@@ -5096,81 +5144,81 @@
         <v>33</v>
       </c>
     </row>
-    <row r="36" spans="1:40">
+    <row r="36" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A36" s="4" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="B36" s="5">
-        <v>680.6</v>
+        <v>5959</v>
       </c>
       <c r="C36" s="5">
-        <v>22.98</v>
-      </c>
-      <c r="D36" s="5">
-        <v>15.24</v>
+        <v>95.575000000000003</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>42</v>
       </c>
       <c r="E36" s="5">
-        <v>15541</v>
+        <v>65873</v>
       </c>
       <c r="F36" s="5">
-        <v>1.55</v>
+        <v>1.97</v>
       </c>
       <c r="G36" s="5">
-        <v>299</v>
+        <v>1090</v>
       </c>
       <c r="H36" s="5">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="I36" s="5">
-        <v>30</v>
+        <v>75.5</v>
       </c>
       <c r="J36" s="5">
-        <v>912.5</v>
+        <v>2296.458333</v>
       </c>
       <c r="K36" s="6">
-        <v>1003</v>
+        <v>2555</v>
       </c>
       <c r="L36" s="6">
-        <v>1826</v>
+        <v>1520</v>
       </c>
       <c r="M36" s="6">
-        <v>168</v>
+        <v>224</v>
       </c>
       <c r="N36" s="5">
         <v>1</v>
       </c>
       <c r="O36" s="5">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="P36" s="6">
-        <v>351</v>
+        <v>288</v>
       </c>
       <c r="Q36" s="6">
-        <v>176</v>
+        <v>391.33333329999999</v>
       </c>
       <c r="R36" s="5">
-        <v>138.6</v>
-      </c>
-      <c r="S36" s="5">
-        <v>410.5</v>
-      </c>
-      <c r="T36" s="5" t="s">
-        <v>42</v>
+        <v>393</v>
+      </c>
+      <c r="S36" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="T36" s="5">
+        <v>3.53</v>
       </c>
       <c r="U36" s="5">
-        <v>736.5</v>
+        <v>1905.125</v>
       </c>
       <c r="V36" s="5">
-        <v>157</v>
+        <v>400</v>
       </c>
       <c r="W36" s="5">
-        <v>28</v>
+        <v>79</v>
       </c>
       <c r="X36" s="6">
         <v>3</v>
       </c>
       <c r="Y36" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z36" s="6">
         <v>2</v>
@@ -5179,10 +5227,10 @@
         <v>42</v>
       </c>
       <c r="AB36" s="5">
-        <v>36.090000000000003</v>
+        <v>33</v>
       </c>
       <c r="AC36" s="5">
-        <v>322</v>
+        <v>536.39</v>
       </c>
       <c r="AD36" s="5" t="s">
         <v>42</v>
@@ -5190,8 +5238,8 @@
       <c r="AE36" s="6">
         <v>2</v>
       </c>
-      <c r="AF36" s="5">
-        <v>738.81</v>
+      <c r="AF36" s="5" t="s">
+        <v>42</v>
       </c>
       <c r="AG36" s="5" t="s">
         <v>42</v>
@@ -5202,23 +5250,23 @@
       <c r="AI36" s="6">
         <v>3</v>
       </c>
-      <c r="AJ36" s="5">
-        <v>0.25</v>
-      </c>
-      <c r="AK36" s="5">
-        <v>478630</v>
-      </c>
-      <c r="AL36" s="5">
-        <v>117490</v>
+      <c r="AJ36" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AK36" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AL36" s="5" t="s">
+        <v>42</v>
       </c>
       <c r="AM36" s="6" t="s">
         <v>42</v>
       </c>
       <c r="AN36" s="3">
-        <v>34</v>
+        <v>26</v>
       </c>
     </row>
-    <row r="37" spans="1:40">
+    <row r="37" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A37" s="4" t="s">
         <v>77</v>
       </c>
@@ -5340,7 +5388,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="38" spans="1:40">
+    <row r="38" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A38" s="4" t="s">
         <v>78</v>
       </c>
@@ -5462,655 +5510,655 @@
         <v>36</v>
       </c>
     </row>
-    <row r="39" spans="1:40">
+    <row r="39" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A39" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B39" s="5">
+        <v>821.89329999999995</v>
+      </c>
+      <c r="C39" s="5">
+        <v>7.5</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E39" s="5">
+        <v>3282</v>
+      </c>
+      <c r="F39" s="5">
+        <v>1.135</v>
+      </c>
+      <c r="G39" s="5">
+        <v>76.5</v>
+      </c>
+      <c r="H39" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="I39" s="5">
+        <v>19.5</v>
+      </c>
+      <c r="J39" s="5">
+        <v>593.125</v>
+      </c>
+      <c r="K39" s="6">
+        <v>595</v>
+      </c>
+      <c r="L39" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="M39" s="6">
+        <v>163</v>
+      </c>
+      <c r="N39" s="5">
+        <v>1</v>
+      </c>
+      <c r="O39" s="5">
+        <v>1</v>
+      </c>
+      <c r="P39" s="6">
+        <v>365</v>
+      </c>
+      <c r="Q39" s="6">
+        <v>121</v>
+      </c>
+      <c r="R39" s="5">
+        <v>27</v>
+      </c>
+      <c r="S39" s="5">
+        <v>250</v>
+      </c>
+      <c r="T39" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="U39" s="5">
+        <v>472.125</v>
+      </c>
+      <c r="V39" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="W39" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="X39" s="6">
+        <v>1</v>
+      </c>
+      <c r="Y39" s="6">
+        <v>2</v>
+      </c>
+      <c r="Z39" s="6">
+        <v>1</v>
+      </c>
+      <c r="AA39" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB39" s="5">
+        <v>1</v>
+      </c>
+      <c r="AC39" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AD39" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AE39" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF39" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AG39" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH39" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI39" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="AJ39" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AK39" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AL39" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AM39" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="AN39" s="3">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="40" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="A40" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B40" s="5">
+        <v>7992.75</v>
+      </c>
+      <c r="C40" s="5">
+        <v>103.375</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E40" s="5">
+        <v>68733</v>
+      </c>
+      <c r="F40" s="5">
+        <v>1.865</v>
+      </c>
+      <c r="G40" s="5">
+        <v>742</v>
+      </c>
+      <c r="H40" s="5">
+        <v>32.700000000000003</v>
+      </c>
+      <c r="I40" s="5">
+        <v>49.05</v>
+      </c>
+      <c r="J40" s="5">
+        <v>1491.9375</v>
+      </c>
+      <c r="K40" s="6">
+        <v>2525.48</v>
+      </c>
+      <c r="L40" s="6">
+        <v>2525.48</v>
+      </c>
+      <c r="M40" s="6">
+        <v>175</v>
+      </c>
+      <c r="N40" s="5">
+        <v>1.01</v>
+      </c>
+      <c r="O40" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="P40" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q40" s="6">
+        <v>365</v>
+      </c>
+      <c r="R40" s="5">
+        <v>498.58</v>
+      </c>
+      <c r="S40" s="5">
+        <v>2170</v>
+      </c>
+      <c r="T40" s="5">
+        <v>2.61</v>
+      </c>
+      <c r="U40" s="5">
+        <v>1126.9375</v>
+      </c>
+      <c r="V40" s="5">
+        <v>410</v>
+      </c>
+      <c r="W40" s="5">
+        <v>64</v>
+      </c>
+      <c r="X40" s="6">
+        <v>3</v>
+      </c>
+      <c r="Y40" s="6">
+        <v>3</v>
+      </c>
+      <c r="Z40" s="6">
+        <v>2</v>
+      </c>
+      <c r="AA40" s="5">
+        <v>17</v>
+      </c>
+      <c r="AB40" s="5">
+        <v>16</v>
+      </c>
+      <c r="AC40" s="5">
+        <v>521.54999999999995</v>
+      </c>
+      <c r="AD40" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AE40" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF40" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AG40" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH40" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI40" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="AJ40" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AK40" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AL40" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AM40" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="AN40" s="3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="41" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="A41" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B41" s="5">
+        <v>281.44</v>
+      </c>
+      <c r="C41" s="5">
+        <v>6.6333333330000004</v>
+      </c>
+      <c r="D41" s="5">
+        <v>2.69</v>
+      </c>
+      <c r="E41" s="5">
+        <v>3524</v>
+      </c>
+      <c r="F41" s="5">
+        <v>1.2849999999999999</v>
+      </c>
+      <c r="G41" s="5">
+        <v>51.6</v>
+      </c>
+      <c r="H41" s="5">
+        <v>16.399999999999999</v>
+      </c>
+      <c r="I41" s="5">
+        <v>18</v>
+      </c>
+      <c r="J41" s="5">
+        <v>547.5</v>
+      </c>
+      <c r="K41" s="6">
+        <v>380</v>
+      </c>
+      <c r="L41" s="6">
+        <v>365</v>
+      </c>
+      <c r="M41" s="6">
+        <v>165.75</v>
+      </c>
+      <c r="N41" s="5">
+        <v>1.45</v>
+      </c>
+      <c r="O41" s="5">
+        <v>1.5</v>
+      </c>
+      <c r="P41" s="6">
+        <v>234</v>
+      </c>
+      <c r="Q41" s="6">
+        <v>160</v>
+      </c>
+      <c r="R41" s="5">
+        <v>11.175000000000001</v>
+      </c>
+      <c r="S41" s="5">
+        <v>139</v>
+      </c>
+      <c r="T41" s="5">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="U41" s="5">
+        <v>387.5</v>
+      </c>
+      <c r="V41" s="5">
+        <v>1</v>
+      </c>
+      <c r="W41" s="5">
+        <v>15</v>
+      </c>
+      <c r="X41" s="6">
+        <v>1</v>
+      </c>
+      <c r="Y41" s="6">
+        <v>4</v>
+      </c>
+      <c r="Z41" s="6">
+        <v>2</v>
+      </c>
+      <c r="AA41" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB41" s="5">
+        <v>1</v>
+      </c>
+      <c r="AC41" s="5">
+        <v>224.49</v>
+      </c>
+      <c r="AD41" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AE41" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF41" s="5">
+        <v>147.5</v>
+      </c>
+      <c r="AG41" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH41" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI41" s="6">
+        <v>4</v>
+      </c>
+      <c r="AJ41" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AK41" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AL41" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AM41" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="AN41" s="3">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="42" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="A42" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B42" s="5">
+        <v>7102.8333329999996</v>
+      </c>
+      <c r="C42" s="5">
+        <v>89.22</v>
+      </c>
+      <c r="D42" s="5">
+        <v>58</v>
+      </c>
+      <c r="E42" s="8">
+        <v>63482</v>
+      </c>
+      <c r="F42" s="5">
+        <v>1.79</v>
+      </c>
+      <c r="G42" s="5">
+        <v>834</v>
+      </c>
+      <c r="H42" s="5">
+        <v>36</v>
+      </c>
+      <c r="I42" s="5">
+        <v>50</v>
+      </c>
+      <c r="J42" s="5">
+        <v>1520.833333</v>
+      </c>
+      <c r="K42" s="6">
+        <v>1231</v>
+      </c>
+      <c r="L42" s="6">
+        <v>2007</v>
+      </c>
+      <c r="M42" s="6">
+        <v>165.66666670000001</v>
+      </c>
+      <c r="N42" s="5">
+        <v>1</v>
+      </c>
+      <c r="O42" s="5">
+        <v>1</v>
+      </c>
+      <c r="P42" s="6">
+        <v>404.5</v>
+      </c>
+      <c r="Q42" s="6">
+        <v>292.5</v>
+      </c>
+      <c r="R42" s="5">
+        <v>485.82499999999999</v>
+      </c>
+      <c r="S42" s="5">
+        <v>1435</v>
+      </c>
+      <c r="T42" s="5">
+        <v>2.46</v>
+      </c>
+      <c r="U42" s="5">
+        <v>1228.333333</v>
+      </c>
+      <c r="V42" s="5">
+        <v>400</v>
+      </c>
+      <c r="W42" s="5">
+        <v>63</v>
+      </c>
+      <c r="X42" s="6">
+        <v>3</v>
+      </c>
+      <c r="Y42" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z42" s="6">
+        <v>2</v>
+      </c>
+      <c r="AA42" s="5">
+        <v>48</v>
+      </c>
+      <c r="AB42" s="5">
+        <v>38.5</v>
+      </c>
+      <c r="AC42" s="5">
+        <v>555</v>
+      </c>
+      <c r="AD42" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AE42" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF42" s="5">
+        <v>2239</v>
+      </c>
+      <c r="AG42" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH42" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="AI42" s="6">
+        <v>3</v>
+      </c>
+      <c r="AJ42" s="5">
+        <v>0.27</v>
+      </c>
+      <c r="AK42" s="5">
+        <v>422149</v>
+      </c>
+      <c r="AL42" s="5">
+        <v>113783</v>
+      </c>
+      <c r="AM42" s="6">
+        <v>60</v>
+      </c>
+      <c r="AN42" s="3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="43" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="A43" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="B39" s="5">
+      <c r="B43" s="5">
         <v>71.828000000000003</v>
       </c>
-      <c r="C39" s="5">
+      <c r="C43" s="5">
         <v>1.846666667</v>
       </c>
-      <c r="D39" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E39" s="5">
+      <c r="D43" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E43" s="5">
         <v>740</v>
       </c>
-      <c r="F39" s="5">
+      <c r="F43" s="5">
         <v>1.1000000000000001</v>
       </c>
-      <c r="G39" s="5">
+      <c r="G43" s="5">
         <v>11.3</v>
       </c>
-      <c r="H39" s="5">
+      <c r="H43" s="5">
         <v>15.5</v>
       </c>
-      <c r="I39" s="5">
+      <c r="I43" s="5">
         <v>14.83333333</v>
       </c>
-      <c r="J39" s="5">
+      <c r="J43" s="5">
         <v>451.18055550000003</v>
       </c>
-      <c r="K39" s="6">
+      <c r="K43" s="6">
         <v>243</v>
       </c>
-      <c r="L39" s="6">
+      <c r="L43" s="6">
         <v>243</v>
       </c>
-      <c r="M39" s="6">
+      <c r="M43" s="6">
         <v>60.75</v>
       </c>
-      <c r="N39" s="5">
-        <v>2</v>
-      </c>
-      <c r="O39" s="5">
-        <v>1</v>
-      </c>
-      <c r="P39" s="6">
+      <c r="N43" s="5">
+        <v>2</v>
+      </c>
+      <c r="O43" s="5">
+        <v>1</v>
+      </c>
+      <c r="P43" s="6">
         <v>250</v>
       </c>
-      <c r="Q39" s="6">
+      <c r="Q43" s="6">
         <v>39</v>
       </c>
-      <c r="R39" s="5">
+      <c r="R43" s="5">
         <v>5.5250000000000004</v>
       </c>
-      <c r="S39" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="T39" s="5">
+      <c r="S43" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="T43" s="5">
         <v>0.73</v>
       </c>
-      <c r="U39" s="5">
+      <c r="U43" s="5">
         <v>412.18055550000003</v>
       </c>
-      <c r="V39" s="5">
-        <v>2</v>
-      </c>
-      <c r="W39" s="5">
+      <c r="V43" s="5">
+        <v>2</v>
+      </c>
+      <c r="W43" s="5">
         <v>51</v>
       </c>
-      <c r="X39" s="6">
-        <v>1</v>
-      </c>
-      <c r="Y39" s="6">
+      <c r="X43" s="6">
+        <v>1</v>
+      </c>
+      <c r="Y43" s="6">
         <v>5</v>
       </c>
-      <c r="Z39" s="6">
-        <v>2</v>
-      </c>
-      <c r="AA39" s="5">
+      <c r="Z43" s="6">
+        <v>2</v>
+      </c>
+      <c r="AA43" s="5">
         <v>3.5</v>
       </c>
-      <c r="AB39" s="5">
-        <v>1</v>
-      </c>
-      <c r="AC39" s="5">
+      <c r="AB43" s="5">
+        <v>1</v>
+      </c>
+      <c r="AC43" s="5">
         <v>143.61000000000001</v>
       </c>
-      <c r="AD39" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AE39" s="6">
-        <v>2</v>
-      </c>
-      <c r="AF39" s="5">
+      <c r="AD43" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AE43" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF43" s="5">
         <v>84.07</v>
       </c>
-      <c r="AG39" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AH39" s="6">
-        <v>1</v>
-      </c>
-      <c r="AI39" s="6">
-        <v>1</v>
-      </c>
-      <c r="AJ39" s="5">
+      <c r="AG43" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH43" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI43" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ43" s="5">
         <v>0.59</v>
       </c>
-      <c r="AK39" s="5">
+      <c r="AK43" s="5">
         <v>190546</v>
       </c>
-      <c r="AL39" s="5">
+      <c r="AL43" s="5">
         <v>112202</v>
       </c>
-      <c r="AM39" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="AN39" s="3">
+      <c r="AM43" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="AN43" s="3">
         <v>37</v>
       </c>
     </row>
-    <row r="40" spans="1:40">
-      <c r="A40" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="B40" s="5">
-        <v>433.25</v>
-      </c>
-      <c r="C40" s="5">
-        <v>6.4333333330000002</v>
-      </c>
-      <c r="D40" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E40" s="5">
-        <v>2938</v>
-      </c>
-      <c r="F40" s="5">
-        <v>1.1499999999999999</v>
-      </c>
-      <c r="G40" s="5">
-        <v>83.4</v>
-      </c>
-      <c r="H40" s="5">
-        <v>15</v>
-      </c>
-      <c r="I40" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="J40" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="K40" s="6">
-        <v>365</v>
-      </c>
-      <c r="L40" s="6">
-        <v>365</v>
-      </c>
-      <c r="M40" s="6">
-        <v>70</v>
-      </c>
-      <c r="N40" s="5">
-        <v>2.5</v>
-      </c>
-      <c r="O40" s="5">
-        <v>1</v>
-      </c>
-      <c r="P40" s="6">
-        <v>365</v>
-      </c>
-      <c r="Q40" s="6">
-        <v>45</v>
-      </c>
-      <c r="R40" s="5">
-        <v>14.09</v>
-      </c>
-      <c r="S40" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="T40" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="U40" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="V40" s="5">
-        <v>4.2</v>
-      </c>
-      <c r="W40" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="X40" s="6">
-        <v>1</v>
-      </c>
-      <c r="Y40" s="6">
-        <v>5</v>
-      </c>
-      <c r="Z40" s="6">
-        <v>2</v>
-      </c>
-      <c r="AA40" s="5">
-        <v>1</v>
-      </c>
-      <c r="AB40" s="5">
-        <v>1</v>
-      </c>
-      <c r="AC40" s="5">
-        <v>225</v>
-      </c>
-      <c r="AD40" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AE40" s="6">
-        <v>2</v>
-      </c>
-      <c r="AF40" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AG40" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AH40" s="6">
-        <v>1</v>
-      </c>
-      <c r="AI40" s="6">
-        <v>1</v>
-      </c>
-      <c r="AJ40" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AK40" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AL40" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AM40" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="AN40" s="3">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="41" spans="1:40">
-      <c r="A41" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="B41" s="5">
-        <v>214</v>
-      </c>
-      <c r="C41" s="5">
-        <v>3.0133333329999998</v>
-      </c>
-      <c r="D41" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E41" s="5">
-        <v>1221</v>
-      </c>
-      <c r="F41" s="5">
-        <v>1.1100000000000001</v>
-      </c>
-      <c r="G41" s="5">
-        <v>24.6</v>
-      </c>
-      <c r="H41" s="5">
-        <v>19.25</v>
-      </c>
-      <c r="I41" s="5">
-        <v>14.33333333</v>
-      </c>
-      <c r="J41" s="5">
-        <v>435.97222210000001</v>
-      </c>
-      <c r="K41" s="6">
-        <v>365</v>
-      </c>
-      <c r="L41" s="6">
-        <v>730</v>
-      </c>
-      <c r="M41" s="6">
-        <v>61.666666669999998</v>
-      </c>
-      <c r="N41" s="5">
-        <v>2.25</v>
-      </c>
-      <c r="O41" s="5">
-        <v>1</v>
-      </c>
-      <c r="P41" s="6">
-        <v>365</v>
-      </c>
-      <c r="Q41" s="6">
-        <v>61.5</v>
-      </c>
-      <c r="R41" s="5">
-        <v>19</v>
-      </c>
-      <c r="S41" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="T41" s="5">
-        <v>0.86</v>
-      </c>
-      <c r="U41" s="5">
-        <v>374.47222210000001</v>
-      </c>
-      <c r="V41" s="5">
-        <v>4</v>
-      </c>
-      <c r="W41" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="X41" s="6">
-        <v>1</v>
-      </c>
-      <c r="Y41" s="6">
-        <v>5</v>
-      </c>
-      <c r="Z41" s="6">
-        <v>2</v>
-      </c>
-      <c r="AA41" s="5">
-        <v>1</v>
-      </c>
-      <c r="AB41" s="5">
-        <v>1</v>
-      </c>
-      <c r="AC41" s="5">
-        <v>225</v>
-      </c>
-      <c r="AD41" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AE41" s="6">
-        <v>2</v>
-      </c>
-      <c r="AF41" s="5">
-        <v>148.1</v>
-      </c>
-      <c r="AG41" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AH41" s="6">
-        <v>1</v>
-      </c>
-      <c r="AI41" s="6">
-        <v>1</v>
-      </c>
-      <c r="AJ41" s="5">
-        <v>0.59</v>
-      </c>
-      <c r="AK41" s="5">
-        <v>186209</v>
-      </c>
-      <c r="AL41" s="5">
-        <v>109648</v>
-      </c>
-      <c r="AM41" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="AN41" s="3">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="42" spans="1:40">
-      <c r="A42" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="B42" s="5">
-        <v>1200.1428000000001</v>
-      </c>
-      <c r="C42" s="5">
-        <v>10.647500000000001</v>
-      </c>
-      <c r="D42" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E42" s="5">
-        <v>4813</v>
-      </c>
-      <c r="F42" s="5">
-        <v>1.2549999999999999</v>
-      </c>
-      <c r="G42" s="5">
-        <v>172</v>
-      </c>
-      <c r="H42" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="I42" s="5">
-        <v>30.9</v>
-      </c>
-      <c r="J42" s="5">
-        <v>939.875</v>
-      </c>
-      <c r="K42" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="L42" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="M42" s="6">
-        <v>135</v>
-      </c>
-      <c r="N42" s="5">
-        <v>1</v>
-      </c>
-      <c r="O42" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="P42" s="6">
-        <v>365</v>
-      </c>
-      <c r="Q42" s="6">
-        <v>165</v>
-      </c>
-      <c r="R42" s="5">
-        <v>29</v>
-      </c>
-      <c r="S42" s="5">
-        <v>500</v>
-      </c>
-      <c r="T42" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="U42" s="5">
-        <v>774.875</v>
-      </c>
-      <c r="V42" s="5">
-        <v>1.5</v>
-      </c>
-      <c r="W42" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="X42" s="6">
-        <v>1</v>
-      </c>
-      <c r="Y42" s="6">
-        <v>3</v>
-      </c>
-      <c r="Z42" s="6">
-        <v>1</v>
-      </c>
-      <c r="AA42" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AB42" s="5">
-        <v>2</v>
-      </c>
-      <c r="AC42" s="5">
-        <v>275</v>
-      </c>
-      <c r="AD42" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AE42" s="6">
-        <v>2</v>
-      </c>
-      <c r="AF42" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AG42" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AH42" s="6">
-        <v>2</v>
-      </c>
-      <c r="AI42" s="6">
-        <v>2</v>
-      </c>
-      <c r="AJ42" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AK42" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AL42" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AM42" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="AN42" s="3">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="43" spans="1:40">
-      <c r="A43" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="B43" s="5">
-        <v>832.33299999999997</v>
-      </c>
-      <c r="C43" s="5">
-        <v>9.6850000000000005</v>
-      </c>
-      <c r="D43" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E43" s="5">
-        <v>4443</v>
-      </c>
-      <c r="F43" s="5">
-        <v>1.145</v>
-      </c>
-      <c r="G43" s="5">
-        <v>73.7</v>
-      </c>
-      <c r="H43" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="I43" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="J43" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="K43" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="L43" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="M43" s="6">
-        <v>135</v>
-      </c>
-      <c r="N43" s="5">
-        <v>1</v>
-      </c>
-      <c r="O43" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="P43" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q43" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="R43" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="S43" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="T43" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="U43" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="V43" s="5">
-        <v>1.5</v>
-      </c>
-      <c r="W43" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="X43" s="6">
-        <v>2</v>
-      </c>
-      <c r="Y43" s="6">
-        <v>1</v>
-      </c>
-      <c r="Z43" s="6">
-        <v>1</v>
-      </c>
-      <c r="AA43" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AB43" s="5">
-        <v>3</v>
-      </c>
-      <c r="AC43" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AD43" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AE43" s="6">
-        <v>2</v>
-      </c>
-      <c r="AF43" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AG43" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AH43" s="6">
-        <v>1</v>
-      </c>
-      <c r="AI43" s="6">
-        <v>2</v>
-      </c>
-      <c r="AJ43" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AK43" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AL43" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AM43" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="AN43" s="3">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="44" spans="1:40">
+    <row r="44" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A44" s="4" t="s">
-        <v>84</v>
+        <v>52</v>
       </c>
       <c r="B44" s="5">
-        <v>3547.125</v>
+        <v>1381</v>
       </c>
       <c r="C44" s="5">
-        <v>26.9</v>
+        <v>39.1</v>
       </c>
       <c r="D44" s="5" t="s">
         <v>42</v>
       </c>
       <c r="E44" s="5">
-        <v>13170</v>
+        <v>26427</v>
       </c>
       <c r="F44" s="5">
-        <v>1.345</v>
+        <v>1.74</v>
       </c>
       <c r="G44" s="5">
-        <v>231</v>
-      </c>
-      <c r="H44" s="5">
-        <v>20.6</v>
+        <v>262</v>
+      </c>
+      <c r="H44" s="5" t="s">
+        <v>42</v>
       </c>
       <c r="I44" s="5">
-        <v>43.466666670000002</v>
+        <v>52.56</v>
       </c>
       <c r="J44" s="5">
-        <v>1322.1111109999999</v>
+        <v>1598.7</v>
       </c>
       <c r="K44" s="6">
-        <v>912</v>
+        <v>1395</v>
       </c>
       <c r="L44" s="6">
-        <v>912</v>
+        <v>2008</v>
       </c>
       <c r="M44" s="6">
-        <v>146.75</v>
+        <v>164.5</v>
       </c>
       <c r="N44" s="5">
         <v>1</v>
@@ -6119,28 +6167,28 @@
         <v>1</v>
       </c>
       <c r="P44" s="6">
-        <v>448.5</v>
+        <v>730.5</v>
       </c>
       <c r="Q44" s="6">
-        <v>173.25</v>
+        <v>168.33333329999999</v>
       </c>
       <c r="R44" s="5">
-        <v>94.15</v>
+        <v>187.1</v>
       </c>
       <c r="S44" s="5">
-        <v>1000</v>
+        <v>450</v>
       </c>
       <c r="T44" s="5">
-        <v>2.62</v>
+        <v>3.44</v>
       </c>
       <c r="U44" s="5">
-        <v>1148.8611109999999</v>
+        <v>1430.366667</v>
       </c>
       <c r="V44" s="5">
-        <v>8.5</v>
-      </c>
-      <c r="W44" s="5">
-        <v>41</v>
+        <v>120</v>
+      </c>
+      <c r="W44" s="5" t="s">
+        <v>42</v>
       </c>
       <c r="X44" s="6">
         <v>3</v>
@@ -6149,16 +6197,16 @@
         <v>3</v>
       </c>
       <c r="Z44" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA44" s="5">
-        <v>7.5</v>
+        <v>66.5</v>
       </c>
       <c r="AB44" s="5">
-        <v>6.3</v>
+        <v>91.2</v>
       </c>
       <c r="AC44" s="5">
-        <v>472.49</v>
+        <v>354.99</v>
       </c>
       <c r="AD44" s="5" t="s">
         <v>42</v>
@@ -6166,8 +6214,8 @@
       <c r="AE44" s="6">
         <v>2</v>
       </c>
-      <c r="AF44" s="5">
-        <v>670</v>
+      <c r="AF44" s="5" t="s">
+        <v>42</v>
       </c>
       <c r="AG44" s="5" t="s">
         <v>42</v>
@@ -6191,376 +6239,376 @@
         <v>42</v>
       </c>
       <c r="AN44" s="3">
-        <v>42</v>
+        <v>11</v>
       </c>
     </row>
-    <row r="45" spans="1:40">
+    <row r="45" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A45" s="4" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="B45" s="5">
-        <v>7410.8333000000002</v>
+        <v>828.1875</v>
       </c>
       <c r="C45" s="5">
-        <v>37.35</v>
-      </c>
-      <c r="D45" s="5" t="s">
-        <v>42</v>
+        <v>11.733333330000001</v>
+      </c>
+      <c r="D45" s="5">
+        <v>4</v>
       </c>
       <c r="E45" s="5">
-        <v>20114</v>
+        <v>6.1920000000000002</v>
       </c>
       <c r="F45" s="5">
-        <v>1.4550000000000001</v>
+        <v>1.2050000000000001</v>
       </c>
       <c r="G45" s="5">
-        <v>330</v>
+        <v>142</v>
       </c>
       <c r="H45" s="5">
-        <v>34.5</v>
+        <v>26.5</v>
       </c>
       <c r="I45" s="5">
-        <v>84</v>
+        <v>25.3</v>
       </c>
       <c r="J45" s="5">
-        <v>2555</v>
+        <v>769.54166669999995</v>
       </c>
       <c r="K45" s="6">
-        <v>2008</v>
-      </c>
-      <c r="L45" s="6">
-        <v>2008</v>
+        <v>578</v>
+      </c>
+      <c r="L45" s="6" t="s">
+        <v>42</v>
       </c>
       <c r="M45" s="6">
-        <v>159.5</v>
+        <v>192</v>
       </c>
       <c r="N45" s="5">
         <v>1</v>
       </c>
       <c r="O45" s="5">
-        <v>0.42</v>
+        <v>1</v>
       </c>
       <c r="P45" s="6">
-        <v>906</v>
+        <v>428.5</v>
       </c>
       <c r="Q45" s="6">
-        <v>364.33333329999999</v>
+        <v>157.25</v>
       </c>
       <c r="R45" s="5">
+        <v>46.16</v>
+      </c>
+      <c r="S45" s="5">
+        <v>520</v>
+      </c>
+      <c r="T45" s="5">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="U45" s="5">
+        <v>612.29166669999995</v>
+      </c>
+      <c r="V45" s="5">
+        <v>5</v>
+      </c>
+      <c r="W45" s="5">
+        <v>60</v>
+      </c>
+      <c r="X45" s="6">
+        <v>1</v>
+      </c>
+      <c r="Y45" s="6">
+        <v>6</v>
+      </c>
+      <c r="Z45" s="6">
+        <v>2</v>
+      </c>
+      <c r="AA45" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB45" s="5">
+        <v>1</v>
+      </c>
+      <c r="AC45" s="5">
         <v>300</v>
       </c>
-      <c r="S45" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="T45" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="U45" s="5">
-        <v>2190.666667</v>
-      </c>
-      <c r="V45" s="5">
-        <v>18</v>
-      </c>
-      <c r="W45" s="5">
-        <v>43</v>
-      </c>
-      <c r="X45" s="6">
+      <c r="AD45" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AE45" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF45" s="5">
+        <v>240</v>
+      </c>
+      <c r="AG45" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH45" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI45" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ45" s="5">
+        <v>0.49</v>
+      </c>
+      <c r="AK45" s="5">
+        <v>109648</v>
+      </c>
+      <c r="AL45" s="5">
+        <v>53703</v>
+      </c>
+      <c r="AM45" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="AN45" s="3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="46" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="A46" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B46" s="5">
+        <v>952.428</v>
+      </c>
+      <c r="C46" s="5">
+        <v>10.6</v>
+      </c>
+      <c r="D46" s="5">
+        <v>4</v>
+      </c>
+      <c r="E46" s="5">
+        <v>4723</v>
+      </c>
+      <c r="F46" s="5">
+        <v>1.2549999999999999</v>
+      </c>
+      <c r="G46" s="5">
+        <v>147</v>
+      </c>
+      <c r="H46" s="5">
+        <v>15.66</v>
+      </c>
+      <c r="I46" s="5">
+        <v>23</v>
+      </c>
+      <c r="J46" s="5">
+        <v>699.58333330000005</v>
+      </c>
+      <c r="K46" s="6">
+        <v>430</v>
+      </c>
+      <c r="L46" s="6">
+        <v>639</v>
+      </c>
+      <c r="M46" s="6">
+        <v>134</v>
+      </c>
+      <c r="N46" s="5">
+        <v>1.5333333330000001</v>
+      </c>
+      <c r="O46" s="5">
+        <v>1</v>
+      </c>
+      <c r="P46" s="6">
+        <v>281.33333329999999</v>
+      </c>
+      <c r="Q46" s="6">
+        <v>121</v>
+      </c>
+      <c r="R46" s="5">
+        <v>43.96</v>
+      </c>
+      <c r="S46" s="5">
+        <v>500</v>
+      </c>
+      <c r="T46" s="5">
+        <v>1.47</v>
+      </c>
+      <c r="U46" s="5">
+        <v>578.58333330000005</v>
+      </c>
+      <c r="V46" s="5">
+        <v>10</v>
+      </c>
+      <c r="W46" s="5">
+        <v>27</v>
+      </c>
+      <c r="X46" s="6">
+        <v>1</v>
+      </c>
+      <c r="Y46" s="6">
+        <v>5</v>
+      </c>
+      <c r="Z46" s="6">
+        <v>2</v>
+      </c>
+      <c r="AA46" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB46" s="5">
+        <v>3.5</v>
+      </c>
+      <c r="AC46" s="5">
+        <v>307</v>
+      </c>
+      <c r="AD46" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AE46" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF46" s="5">
+        <v>457.15</v>
+      </c>
+      <c r="AG46" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH46" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="AI46" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ46" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AK46" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AL46" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AM46" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="AN46" s="3">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="47" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="A47" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B47" s="5">
+        <v>41057.090909999999</v>
+      </c>
+      <c r="C47" s="5">
+        <v>392.06</v>
+      </c>
+      <c r="D47" s="5">
+        <v>128</v>
+      </c>
+      <c r="E47" s="8">
+        <v>291592</v>
+      </c>
+      <c r="F47" s="5">
+        <v>2.4550000000000001</v>
+      </c>
+      <c r="G47" s="5">
+        <v>1899</v>
+      </c>
+      <c r="H47" s="5">
+        <v>59.4</v>
+      </c>
+      <c r="I47" s="5">
+        <v>164.8</v>
+      </c>
+      <c r="J47" s="5">
+        <v>5012.6666670000004</v>
+      </c>
+      <c r="K47" s="6">
+        <v>3376</v>
+      </c>
+      <c r="L47" s="6">
+        <v>2920</v>
+      </c>
+      <c r="M47" s="6">
+        <v>234</v>
+      </c>
+      <c r="N47" s="5">
+        <v>1</v>
+      </c>
+      <c r="O47" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="P47" s="6">
+        <v>1320</v>
+      </c>
+      <c r="Q47" s="6">
+        <v>1579.5</v>
+      </c>
+      <c r="R47" s="5">
+        <v>1736.25</v>
+      </c>
+      <c r="S47" s="5">
+        <v>8500</v>
+      </c>
+      <c r="T47" s="5">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="U47" s="5">
+        <v>3433.166667</v>
+      </c>
+      <c r="V47" s="5">
+        <v>1085</v>
+      </c>
+      <c r="W47" s="5">
+        <v>66</v>
+      </c>
+      <c r="X47" s="6">
         <v>3</v>
       </c>
-      <c r="Y45" s="6">
-        <v>4</v>
-      </c>
-      <c r="Z45" s="6">
-        <v>1</v>
-      </c>
-      <c r="AA45" s="5">
-        <v>3.5</v>
-      </c>
-      <c r="AB45" s="5">
-        <v>3.1</v>
-      </c>
-      <c r="AC45" s="5">
-        <v>734.99</v>
-      </c>
-      <c r="AD45" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AE45" s="6">
-        <v>2</v>
-      </c>
-      <c r="AF45" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AG45" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AH45" s="6">
-        <v>1</v>
-      </c>
-      <c r="AI45" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="AJ45" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AK45" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AL45" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AM45" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="AN45" s="3">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="46" spans="1:40">
-      <c r="A46" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="B46" s="5">
-        <v>2640.2849999999999</v>
-      </c>
-      <c r="C46" s="5">
-        <v>44.887500000000003</v>
-      </c>
-      <c r="D46" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E46" s="5">
-        <v>22127</v>
-      </c>
-      <c r="F46" s="5">
-        <v>1.25</v>
-      </c>
-      <c r="G46" s="5">
-        <v>392</v>
-      </c>
-      <c r="H46" s="5">
-        <v>24.25</v>
-      </c>
-      <c r="I46" s="5">
-        <v>35.5</v>
-      </c>
-      <c r="J46" s="5">
-        <v>1079.791667</v>
-      </c>
-      <c r="K46" s="6">
-        <v>882</v>
-      </c>
-      <c r="L46" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="M46" s="6">
-        <v>164.5</v>
-      </c>
-      <c r="N46" s="5">
-        <v>1</v>
-      </c>
-      <c r="O46" s="5">
-        <v>1</v>
-      </c>
-      <c r="P46" s="6">
-        <v>756</v>
-      </c>
-      <c r="Q46" s="6">
-        <v>244</v>
-      </c>
-      <c r="R46" s="5">
-        <v>119.33333330000001</v>
-      </c>
-      <c r="S46" s="5">
-        <v>1535</v>
-      </c>
-      <c r="T46" s="5">
-        <v>2.04</v>
-      </c>
-      <c r="U46" s="5">
-        <v>835.79166669999995</v>
-      </c>
-      <c r="V46" s="5">
-        <v>11</v>
-      </c>
-      <c r="W46" s="5">
+      <c r="Y47" s="6">
+        <v>6</v>
+      </c>
+      <c r="Z47" s="6">
+        <v>2</v>
+      </c>
+      <c r="AA47" s="5">
+        <v>45</v>
+      </c>
+      <c r="AB47" s="5">
+        <v>45</v>
+      </c>
+      <c r="AC47" s="5">
+        <v>796.09</v>
+      </c>
+      <c r="AD47" s="5">
         <v>0</v>
       </c>
-      <c r="X46" s="6">
-        <v>1</v>
-      </c>
-      <c r="Y46" s="6">
-        <v>6</v>
-      </c>
-      <c r="Z46" s="6">
-        <v>2</v>
-      </c>
-      <c r="AA46" s="5">
-        <v>1</v>
-      </c>
-      <c r="AB46" s="5">
-        <v>1</v>
-      </c>
-      <c r="AC46" s="5">
-        <v>400</v>
-      </c>
-      <c r="AD46" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AE46" s="6">
-        <v>2</v>
-      </c>
-      <c r="AF46" s="5">
-        <v>1393.9</v>
-      </c>
-      <c r="AG46" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AH46" s="6">
-        <v>2</v>
-      </c>
-      <c r="AI46" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="AJ46" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AK46" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AL46" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AM46" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="AN46" s="3">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="47" spans="1:40">
-      <c r="A47" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B47" s="5">
-        <v>1933.8</v>
-      </c>
-      <c r="C47" s="5">
-        <v>28.1</v>
-      </c>
-      <c r="D47" s="5">
-        <v>10.69</v>
-      </c>
-      <c r="E47" s="5">
-        <v>12207</v>
-      </c>
-      <c r="F47" s="5">
-        <v>1.46</v>
-      </c>
-      <c r="G47" s="5">
-        <v>194</v>
-      </c>
-      <c r="H47" s="5">
-        <v>36</v>
-      </c>
-      <c r="I47" s="5">
-        <v>29.875</v>
-      </c>
-      <c r="J47" s="5">
-        <v>908.69791669999995</v>
-      </c>
-      <c r="K47" s="6">
-        <v>548</v>
-      </c>
-      <c r="L47" s="6">
-        <v>548</v>
-      </c>
-      <c r="M47" s="6">
-        <v>120</v>
-      </c>
-      <c r="N47" s="5">
-        <v>1</v>
-      </c>
-      <c r="O47" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="P47" s="6">
-        <v>730</v>
-      </c>
-      <c r="Q47" s="6">
-        <v>159</v>
-      </c>
-      <c r="R47" s="5">
-        <v>75.7</v>
-      </c>
-      <c r="S47" s="5">
-        <v>1350</v>
-      </c>
-      <c r="T47" s="5">
-        <v>1.46</v>
-      </c>
-      <c r="U47" s="5">
-        <v>749.69791669999995</v>
-      </c>
-      <c r="V47" s="5">
-        <v>8.75</v>
-      </c>
-      <c r="W47" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="X47" s="6">
-        <v>2</v>
-      </c>
-      <c r="Y47" s="6">
-        <v>4</v>
-      </c>
-      <c r="Z47" s="6">
-        <v>2</v>
-      </c>
-      <c r="AA47" s="5">
-        <v>9.25</v>
-      </c>
-      <c r="AB47" s="5">
-        <v>9.15</v>
-      </c>
-      <c r="AC47" s="5">
-        <v>469.62</v>
-      </c>
-      <c r="AD47" s="5" t="s">
-        <v>42</v>
-      </c>
       <c r="AE47" s="6">
         <v>2</v>
       </c>
-      <c r="AF47" s="5" t="s">
-        <v>42</v>
+      <c r="AF47" s="5">
+        <v>9000</v>
       </c>
       <c r="AG47" s="5" t="s">
         <v>42</v>
       </c>
       <c r="AH47" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI47" s="6">
         <v>3</v>
       </c>
-      <c r="AJ47" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AK47" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AL47" s="5" t="s">
-        <v>42</v>
+      <c r="AJ47" s="5">
+        <v>0.59</v>
+      </c>
+      <c r="AK47" s="5">
+        <v>208930</v>
+      </c>
+      <c r="AL47" s="5">
+        <v>123027</v>
       </c>
       <c r="AM47" s="6" t="s">
         <v>42</v>
       </c>
       <c r="AN47" s="3">
-        <v>45</v>
+        <v>20</v>
       </c>
     </row>
-    <row r="48" spans="1:40">
+    <row r="48" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A48" s="4" t="s">
         <v>88</v>
       </c>
@@ -6682,7 +6730,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="49" spans="1:40">
+    <row r="49" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A49" s="4" t="s">
         <v>89</v>
       </c>
@@ -6804,93 +6852,93 @@
         <v>47</v>
       </c>
     </row>
-    <row r="50" spans="1:40">
+    <row r="50" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A50" s="4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B50" s="5">
-        <v>3344.857</v>
+        <v>1008.4285</v>
       </c>
       <c r="C50" s="5">
-        <v>49.825000000000003</v>
-      </c>
-      <c r="D50" s="5">
-        <v>10.59</v>
+        <v>13.54</v>
+      </c>
+      <c r="D50" s="5" t="s">
+        <v>42</v>
       </c>
       <c r="E50" s="5">
-        <v>15293</v>
+        <v>6683</v>
       </c>
       <c r="F50" s="5">
-        <v>1.3149999999999999</v>
+        <v>1.2649999999999999</v>
       </c>
       <c r="G50" s="5">
-        <v>299</v>
+        <v>127</v>
       </c>
       <c r="H50" s="5">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="I50" s="5">
-        <v>23.3</v>
+        <v>24.55</v>
       </c>
       <c r="J50" s="5">
-        <v>708.70833330000005</v>
+        <v>746.72916669999995</v>
       </c>
       <c r="K50" s="6">
-        <v>604</v>
+        <v>547</v>
       </c>
       <c r="L50" s="6">
-        <v>608</v>
+        <v>547</v>
       </c>
       <c r="M50" s="6">
-        <v>119.5</v>
+        <v>186</v>
       </c>
       <c r="N50" s="5">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="O50" s="5">
         <v>1</v>
       </c>
       <c r="P50" s="6">
-        <v>365</v>
+        <v>304</v>
       </c>
       <c r="Q50" s="6">
-        <v>109.25</v>
+        <v>142.25</v>
       </c>
       <c r="R50" s="5">
-        <v>88.2</v>
-      </c>
-      <c r="S50" s="5">
-        <v>2696.5</v>
-      </c>
-      <c r="T50" s="5" t="s">
-        <v>42</v>
+        <v>40.549999999999997</v>
+      </c>
+      <c r="S50" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="T50" s="5">
+        <v>1.0900000000000001</v>
       </c>
       <c r="U50" s="5">
-        <v>599.45833330000005</v>
+        <v>604.47916669999995</v>
       </c>
       <c r="V50" s="5">
-        <v>25.8</v>
+        <v>12</v>
       </c>
       <c r="W50" s="5">
-        <v>73.900000000000006</v>
+        <v>65</v>
       </c>
       <c r="X50" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y50" s="6">
         <v>4</v>
       </c>
       <c r="Z50" s="6">
-        <v>1</v>
-      </c>
-      <c r="AA50" s="5">
-        <v>3.5</v>
+        <v>2</v>
+      </c>
+      <c r="AA50" s="5" t="s">
+        <v>42</v>
       </c>
       <c r="AB50" s="5">
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="AC50" s="5">
-        <v>547.35</v>
+        <v>320</v>
       </c>
       <c r="AD50" s="5" t="s">
         <v>42</v>
@@ -6899,852 +6947,852 @@
         <v>2</v>
       </c>
       <c r="AF50" s="5">
-        <v>603.6</v>
+        <v>347.82</v>
       </c>
       <c r="AG50" s="5" t="s">
         <v>42</v>
       </c>
       <c r="AH50" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI50" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ50" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AK50" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AL50" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AM50" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="AN50" s="3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="51" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="A51" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B51" s="5">
+        <v>7854.8333329999996</v>
+      </c>
+      <c r="C51" s="5">
+        <v>76.75</v>
+      </c>
+      <c r="D51" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E51" s="5">
+        <v>50906</v>
+      </c>
+      <c r="F51" s="5">
+        <v>1.8049999999999999</v>
+      </c>
+      <c r="G51" s="5">
+        <v>455</v>
+      </c>
+      <c r="H51" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="I51" s="5">
+        <v>45.45</v>
+      </c>
+      <c r="J51" s="5">
+        <v>1382.4375</v>
+      </c>
+      <c r="K51" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="L51" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="M51" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="N51" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="O51" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="P51" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q51" s="6">
+        <v>656.2</v>
+      </c>
+      <c r="R51" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="S51" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="T51" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="U51" s="5">
+        <v>726.23749999999995</v>
+      </c>
+      <c r="V51" s="5">
+        <v>71</v>
+      </c>
+      <c r="W51" s="5">
+        <v>26</v>
+      </c>
+      <c r="X51" s="6">
         <v>3</v>
       </c>
-      <c r="AJ50" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AK50" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AL50" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AM50" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="AN50" s="3">
+      <c r="Y51" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z51" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA51" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB51" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="AC51" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AD51" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AE51" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF51" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AG51" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH51" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI51" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="AJ51" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AK51" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AL51" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AM51" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="AN51" s="3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="52" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="A52" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B52" s="5">
+        <v>3547.125</v>
+      </c>
+      <c r="C52" s="5">
+        <v>26.9</v>
+      </c>
+      <c r="D52" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E52" s="5">
+        <v>13170</v>
+      </c>
+      <c r="F52" s="5">
+        <v>1.345</v>
+      </c>
+      <c r="G52" s="5">
+        <v>231</v>
+      </c>
+      <c r="H52" s="5">
+        <v>20.6</v>
+      </c>
+      <c r="I52" s="5">
+        <v>43.466666670000002</v>
+      </c>
+      <c r="J52" s="5">
+        <v>1322.1111109999999</v>
+      </c>
+      <c r="K52" s="6">
+        <v>912</v>
+      </c>
+      <c r="L52" s="6">
+        <v>912</v>
+      </c>
+      <c r="M52" s="6">
+        <v>146.75</v>
+      </c>
+      <c r="N52" s="5">
+        <v>1</v>
+      </c>
+      <c r="O52" s="5">
+        <v>1</v>
+      </c>
+      <c r="P52" s="6">
+        <v>448.5</v>
+      </c>
+      <c r="Q52" s="6">
+        <v>173.25</v>
+      </c>
+      <c r="R52" s="5">
+        <v>94.15</v>
+      </c>
+      <c r="S52" s="5">
+        <v>1000</v>
+      </c>
+      <c r="T52" s="5">
+        <v>2.62</v>
+      </c>
+      <c r="U52" s="5">
+        <v>1148.8611109999999</v>
+      </c>
+      <c r="V52" s="5">
+        <v>8.5</v>
+      </c>
+      <c r="W52" s="5">
+        <v>41</v>
+      </c>
+      <c r="X52" s="6">
+        <v>3</v>
+      </c>
+      <c r="Y52" s="6">
+        <v>3</v>
+      </c>
+      <c r="Z52" s="6">
+        <v>1</v>
+      </c>
+      <c r="AA52" s="5">
+        <v>7.5</v>
+      </c>
+      <c r="AB52" s="5">
+        <v>6.3</v>
+      </c>
+      <c r="AC52" s="5">
+        <v>472.49</v>
+      </c>
+      <c r="AD52" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AE52" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF52" s="5">
+        <v>670</v>
+      </c>
+      <c r="AG52" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH52" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI52" s="6">
+        <v>3</v>
+      </c>
+      <c r="AJ52" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AK52" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AL52" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AM52" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="AN52" s="3">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="53" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="A53" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B53" s="5">
+        <v>8481.6666669999995</v>
+      </c>
+      <c r="C53" s="5">
+        <v>84.833333330000002</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E53" s="5">
+        <v>48763</v>
+      </c>
+      <c r="F53" s="5">
+        <v>1.635</v>
+      </c>
+      <c r="G53" s="5">
+        <v>911</v>
+      </c>
+      <c r="H53" s="5">
+        <v>30</v>
+      </c>
+      <c r="I53" s="5">
         <v>48</v>
       </c>
+      <c r="J53" s="5">
+        <v>1460</v>
+      </c>
+      <c r="K53" s="6">
+        <v>1460</v>
+      </c>
+      <c r="L53" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="M53" s="6">
+        <v>190.5</v>
+      </c>
+      <c r="N53" s="5">
+        <v>1</v>
+      </c>
+      <c r="O53" s="5">
+        <v>1</v>
+      </c>
+      <c r="P53" s="6">
+        <v>365</v>
+      </c>
+      <c r="Q53" s="6">
+        <v>330</v>
+      </c>
+      <c r="R53" s="5">
+        <v>428.25</v>
+      </c>
+      <c r="S53" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="T53" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="U53" s="5">
+        <v>1130</v>
+      </c>
+      <c r="V53" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="W53" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="X53" s="6">
+        <v>3</v>
+      </c>
+      <c r="Y53" s="6">
+        <v>2</v>
+      </c>
+      <c r="Z53" s="6">
+        <v>1</v>
+      </c>
+      <c r="AA53" s="5">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="AB53" s="5">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="AC53" s="5">
+        <v>326.37</v>
+      </c>
+      <c r="AD53" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AE53" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF53" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AG53" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH53" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI53" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="AJ53" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AK53" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AL53" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AM53" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="AN53" s="3">
+        <v>17</v>
+      </c>
     </row>
-    <row r="51" spans="1:40">
-      <c r="A51" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B51" s="5">
-        <v>821.89329999999995</v>
-      </c>
-      <c r="C51" s="5">
-        <v>7.5</v>
-      </c>
-      <c r="D51" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E51" s="5">
-        <v>3282</v>
-      </c>
-      <c r="F51" s="5">
-        <v>1.135</v>
-      </c>
-      <c r="G51" s="5">
-        <v>76.5</v>
-      </c>
-      <c r="H51" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="I51" s="5">
-        <v>19.5</v>
-      </c>
-      <c r="J51" s="5">
-        <v>593.125</v>
-      </c>
-      <c r="K51" s="6">
-        <v>595</v>
-      </c>
-      <c r="L51" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="M51" s="6">
-        <v>163</v>
-      </c>
-      <c r="N51" s="5">
-        <v>1</v>
-      </c>
-      <c r="O51" s="5">
-        <v>1</v>
-      </c>
-      <c r="P51" s="6">
+    <row r="54" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="A54" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B54" s="5">
+        <v>439.2</v>
+      </c>
+      <c r="C54" s="5">
+        <v>10.5</v>
+      </c>
+      <c r="D54" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E54" s="5">
+        <v>5883</v>
+      </c>
+      <c r="F54" s="5">
+        <v>1.1950000000000001</v>
+      </c>
+      <c r="G54" s="5">
+        <v>251</v>
+      </c>
+      <c r="H54" s="5">
+        <v>13.3</v>
+      </c>
+      <c r="I54" s="5">
+        <v>24</v>
+      </c>
+      <c r="J54" s="5">
+        <v>730</v>
+      </c>
+      <c r="K54" s="6">
+        <v>608</v>
+      </c>
+      <c r="L54" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="M54" s="6">
+        <v>140.5</v>
+      </c>
+      <c r="N54" s="5">
+        <v>2</v>
+      </c>
+      <c r="O54" s="5">
+        <v>1.4</v>
+      </c>
+      <c r="P54" s="6">
+        <v>240</v>
+      </c>
+      <c r="Q54" s="6">
+        <v>70.5</v>
+      </c>
+      <c r="R54" s="5">
+        <v>38</v>
+      </c>
+      <c r="S54" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="T54" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="U54" s="5">
+        <v>659.5</v>
+      </c>
+      <c r="V54" s="5">
+        <v>9</v>
+      </c>
+      <c r="W54" s="5">
+        <v>69</v>
+      </c>
+      <c r="X54" s="6">
+        <v>3</v>
+      </c>
+      <c r="Y54" s="6">
+        <v>4</v>
+      </c>
+      <c r="Z54" s="6">
+        <v>2</v>
+      </c>
+      <c r="AA54" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB54" s="5">
+        <v>5.55</v>
+      </c>
+      <c r="AC54" s="5">
+        <v>264.20999999999998</v>
+      </c>
+      <c r="AD54" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AE54" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF54" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AG54" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH54" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="AI54" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="AJ54" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AK54" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AL54" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AM54" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="AN54" s="3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="55" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="A55" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B55" s="5">
+        <v>368.83333329999999</v>
+      </c>
+      <c r="C55" s="5">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E55" s="5">
+        <v>5894</v>
+      </c>
+      <c r="F55" s="5">
+        <v>1.1950000000000001</v>
+      </c>
+      <c r="G55" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="H55" s="5">
+        <v>23.08</v>
+      </c>
+      <c r="I55" s="5">
+        <v>22.8</v>
+      </c>
+      <c r="J55" s="5">
+        <v>693.5</v>
+      </c>
+      <c r="K55" s="6">
+        <v>548</v>
+      </c>
+      <c r="L55" s="6">
+        <v>550</v>
+      </c>
+      <c r="M55" s="6">
+        <v>161.5</v>
+      </c>
+      <c r="N55" s="5">
+        <v>1.9</v>
+      </c>
+      <c r="O55" s="5">
+        <v>1</v>
+      </c>
+      <c r="P55" s="6">
+        <v>262</v>
+      </c>
+      <c r="Q55" s="6">
+        <v>52</v>
+      </c>
+      <c r="R55" s="5">
+        <v>41.28</v>
+      </c>
+      <c r="S55" s="5">
+        <v>105</v>
+      </c>
+      <c r="T55" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="U55" s="5">
+        <v>641.5</v>
+      </c>
+      <c r="V55" s="5">
+        <v>32</v>
+      </c>
+      <c r="W55" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="X55" s="6">
+        <v>3</v>
+      </c>
+      <c r="Y55" s="6">
+        <v>4</v>
+      </c>
+      <c r="Z55" s="6">
+        <v>2</v>
+      </c>
+      <c r="AA55" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB55" s="5">
+        <v>7.05</v>
+      </c>
+      <c r="AC55" s="5">
+        <v>239.99</v>
+      </c>
+      <c r="AD55" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AE55" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF55" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AG55" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH55" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI55" s="6">
+        <v>2</v>
+      </c>
+      <c r="AJ55" s="5">
+        <v>0.3</v>
+      </c>
+      <c r="AK55" s="5">
+        <v>328541</v>
+      </c>
+      <c r="AL55" s="5">
+        <v>102329</v>
+      </c>
+      <c r="AM55" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="AN55" s="3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="56" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="A56" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B56" s="5">
+        <v>680.6</v>
+      </c>
+      <c r="C56" s="5">
+        <v>22.98</v>
+      </c>
+      <c r="D56" s="5">
+        <v>15.24</v>
+      </c>
+      <c r="E56" s="5">
+        <v>15541</v>
+      </c>
+      <c r="F56" s="5">
+        <v>1.55</v>
+      </c>
+      <c r="G56" s="5">
+        <v>299</v>
+      </c>
+      <c r="H56" s="5">
+        <v>27</v>
+      </c>
+      <c r="I56" s="5">
+        <v>30</v>
+      </c>
+      <c r="J56" s="5">
+        <v>912.5</v>
+      </c>
+      <c r="K56" s="6">
+        <v>1003</v>
+      </c>
+      <c r="L56" s="6">
+        <v>1826</v>
+      </c>
+      <c r="M56" s="6">
+        <v>168</v>
+      </c>
+      <c r="N56" s="5">
+        <v>1</v>
+      </c>
+      <c r="O56" s="5">
+        <v>1</v>
+      </c>
+      <c r="P56" s="6">
+        <v>351</v>
+      </c>
+      <c r="Q56" s="6">
+        <v>176</v>
+      </c>
+      <c r="R56" s="5">
+        <v>138.6</v>
+      </c>
+      <c r="S56" s="5">
+        <v>410.5</v>
+      </c>
+      <c r="T56" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="U56" s="5">
+        <v>736.5</v>
+      </c>
+      <c r="V56" s="5">
+        <v>157</v>
+      </c>
+      <c r="W56" s="5">
+        <v>28</v>
+      </c>
+      <c r="X56" s="6">
+        <v>3</v>
+      </c>
+      <c r="Y56" s="6">
+        <v>3</v>
+      </c>
+      <c r="Z56" s="6">
+        <v>2</v>
+      </c>
+      <c r="AA56" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB56" s="5">
+        <v>36.090000000000003</v>
+      </c>
+      <c r="AC56" s="5">
+        <v>322</v>
+      </c>
+      <c r="AD56" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AE56" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF56" s="5">
+        <v>738.81</v>
+      </c>
+      <c r="AG56" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH56" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI56" s="6">
+        <v>3</v>
+      </c>
+      <c r="AJ56" s="5">
+        <v>0.25</v>
+      </c>
+      <c r="AK56" s="5">
+        <v>478630</v>
+      </c>
+      <c r="AL56" s="5">
+        <v>117490</v>
+      </c>
+      <c r="AM56" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="AN56" s="3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="57" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="A57" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B57" s="5">
+        <v>3344.857</v>
+      </c>
+      <c r="C57" s="5">
+        <v>49.825000000000003</v>
+      </c>
+      <c r="D57" s="5">
+        <v>10.59</v>
+      </c>
+      <c r="E57" s="5">
+        <v>15293</v>
+      </c>
+      <c r="F57" s="5">
+        <v>1.3149999999999999</v>
+      </c>
+      <c r="G57" s="5">
+        <v>299</v>
+      </c>
+      <c r="H57" s="5">
+        <v>13</v>
+      </c>
+      <c r="I57" s="5">
+        <v>23.3</v>
+      </c>
+      <c r="J57" s="5">
+        <v>708.70833330000005</v>
+      </c>
+      <c r="K57" s="6">
+        <v>604</v>
+      </c>
+      <c r="L57" s="6">
+        <v>608</v>
+      </c>
+      <c r="M57" s="6">
+        <v>119.5</v>
+      </c>
+      <c r="N57" s="5">
+        <v>2.1</v>
+      </c>
+      <c r="O57" s="5">
+        <v>1</v>
+      </c>
+      <c r="P57" s="6">
         <v>365</v>
       </c>
-      <c r="Q51" s="6">
-        <v>121</v>
-      </c>
-      <c r="R51" s="5">
-        <v>27</v>
-      </c>
-      <c r="S51" s="5">
-        <v>250</v>
-      </c>
-      <c r="T51" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="U51" s="5">
-        <v>472.125</v>
-      </c>
-      <c r="V51" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="W51" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="X51" s="6">
-        <v>1</v>
-      </c>
-      <c r="Y51" s="6">
-        <v>2</v>
-      </c>
-      <c r="Z51" s="6">
-        <v>1</v>
-      </c>
-      <c r="AA51" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AB51" s="5">
-        <v>1</v>
-      </c>
-      <c r="AC51" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AD51" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AE51" s="6">
-        <v>2</v>
-      </c>
-      <c r="AF51" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AG51" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AH51" s="6">
-        <v>1</v>
-      </c>
-      <c r="AI51" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="AJ51" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AK51" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AL51" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AM51" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="AN51" s="3">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="52" spans="1:40">
-      <c r="A52" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="B52" s="5">
-        <v>1008.4285</v>
-      </c>
-      <c r="C52" s="5">
-        <v>13.54</v>
-      </c>
-      <c r="D52" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E52" s="5">
-        <v>6683</v>
-      </c>
-      <c r="F52" s="5">
-        <v>1.2649999999999999</v>
-      </c>
-      <c r="G52" s="5">
-        <v>127</v>
-      </c>
-      <c r="H52" s="5">
-        <v>26</v>
-      </c>
-      <c r="I52" s="5">
-        <v>24.55</v>
-      </c>
-      <c r="J52" s="5">
-        <v>746.72916669999995</v>
-      </c>
-      <c r="K52" s="6">
-        <v>547</v>
-      </c>
-      <c r="L52" s="6">
-        <v>547</v>
-      </c>
-      <c r="M52" s="6">
-        <v>186</v>
-      </c>
-      <c r="N52" s="5">
-        <v>1</v>
-      </c>
-      <c r="O52" s="5">
-        <v>1</v>
-      </c>
-      <c r="P52" s="6">
-        <v>304</v>
-      </c>
-      <c r="Q52" s="6">
-        <v>142.25</v>
-      </c>
-      <c r="R52" s="5">
-        <v>40.549999999999997</v>
-      </c>
-      <c r="S52" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="T52" s="5">
-        <v>1.0900000000000001</v>
-      </c>
-      <c r="U52" s="5">
-        <v>604.47916669999995</v>
-      </c>
-      <c r="V52" s="5">
-        <v>12</v>
-      </c>
-      <c r="W52" s="5">
-        <v>65</v>
-      </c>
-      <c r="X52" s="6">
-        <v>1</v>
-      </c>
-      <c r="Y52" s="6">
-        <v>4</v>
-      </c>
-      <c r="Z52" s="6">
-        <v>2</v>
-      </c>
-      <c r="AA52" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AB52" s="5">
-        <v>1</v>
-      </c>
-      <c r="AC52" s="5">
-        <v>320</v>
-      </c>
-      <c r="AD52" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AE52" s="6">
-        <v>2</v>
-      </c>
-      <c r="AF52" s="5">
-        <v>347.82</v>
-      </c>
-      <c r="AG52" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AH52" s="6">
-        <v>1</v>
-      </c>
-      <c r="AI52" s="6">
-        <v>1</v>
-      </c>
-      <c r="AJ52" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AK52" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AL52" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AM52" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="AN52" s="3">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="53" spans="1:40">
-      <c r="A53" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="B53" s="5">
-        <v>281.44</v>
-      </c>
-      <c r="C53" s="5">
-        <v>6.6333333330000004</v>
-      </c>
-      <c r="D53" s="5">
-        <v>2.69</v>
-      </c>
-      <c r="E53" s="5">
-        <v>3524</v>
-      </c>
-      <c r="F53" s="5">
-        <v>1.2849999999999999</v>
-      </c>
-      <c r="G53" s="5">
-        <v>51.6</v>
-      </c>
-      <c r="H53" s="5">
-        <v>16.399999999999999</v>
-      </c>
-      <c r="I53" s="5">
-        <v>18</v>
-      </c>
-      <c r="J53" s="5">
-        <v>547.5</v>
-      </c>
-      <c r="K53" s="6">
-        <v>380</v>
-      </c>
-      <c r="L53" s="6">
-        <v>365</v>
-      </c>
-      <c r="M53" s="6">
-        <v>165.75</v>
-      </c>
-      <c r="N53" s="5">
-        <v>1.45</v>
-      </c>
-      <c r="O53" s="5">
-        <v>1.5</v>
-      </c>
-      <c r="P53" s="6">
-        <v>234</v>
-      </c>
-      <c r="Q53" s="6">
-        <v>160</v>
-      </c>
-      <c r="R53" s="5">
-        <v>11.175000000000001</v>
-      </c>
-      <c r="S53" s="5">
-        <v>139</v>
-      </c>
-      <c r="T53" s="5">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="U53" s="5">
-        <v>387.5</v>
-      </c>
-      <c r="V53" s="5">
-        <v>1</v>
-      </c>
-      <c r="W53" s="5">
-        <v>15</v>
-      </c>
-      <c r="X53" s="6">
-        <v>1</v>
-      </c>
-      <c r="Y53" s="6">
-        <v>4</v>
-      </c>
-      <c r="Z53" s="6">
-        <v>2</v>
-      </c>
-      <c r="AA53" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AB53" s="5">
-        <v>1</v>
-      </c>
-      <c r="AC53" s="5">
-        <v>224.49</v>
-      </c>
-      <c r="AD53" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AE53" s="6">
-        <v>2</v>
-      </c>
-      <c r="AF53" s="5">
-        <v>147.5</v>
-      </c>
-      <c r="AG53" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AH53" s="6">
-        <v>1</v>
-      </c>
-      <c r="AI53" s="6">
-        <v>4</v>
-      </c>
-      <c r="AJ53" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AK53" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AL53" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AM53" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="AN53" s="3">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="54" spans="1:40">
-      <c r="A54" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="B54" s="5">
-        <v>828.1875</v>
-      </c>
-      <c r="C54" s="5">
-        <v>11.733333330000001</v>
-      </c>
-      <c r="D54" s="5">
-        <v>4</v>
-      </c>
-      <c r="E54" s="5">
-        <v>6.1920000000000002</v>
-      </c>
-      <c r="F54" s="5">
-        <v>1.2050000000000001</v>
-      </c>
-      <c r="G54" s="5">
-        <v>142</v>
-      </c>
-      <c r="H54" s="5">
-        <v>26.5</v>
-      </c>
-      <c r="I54" s="5">
-        <v>25.3</v>
-      </c>
-      <c r="J54" s="5">
-        <v>769.54166669999995</v>
-      </c>
-      <c r="K54" s="6">
-        <v>578</v>
-      </c>
-      <c r="L54" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="M54" s="6">
-        <v>192</v>
-      </c>
-      <c r="N54" s="5">
-        <v>1</v>
-      </c>
-      <c r="O54" s="5">
-        <v>1</v>
-      </c>
-      <c r="P54" s="6">
-        <v>428.5</v>
-      </c>
-      <c r="Q54" s="6">
-        <v>157.25</v>
-      </c>
-      <c r="R54" s="5">
-        <v>46.16</v>
-      </c>
-      <c r="S54" s="5">
-        <v>520</v>
-      </c>
-      <c r="T54" s="5">
-        <v>1.0900000000000001</v>
-      </c>
-      <c r="U54" s="5">
-        <v>612.29166669999995</v>
-      </c>
-      <c r="V54" s="5">
-        <v>5</v>
-      </c>
-      <c r="W54" s="5">
-        <v>60</v>
-      </c>
-      <c r="X54" s="6">
-        <v>1</v>
-      </c>
-      <c r="Y54" s="6">
-        <v>6</v>
-      </c>
-      <c r="Z54" s="6">
-        <v>2</v>
-      </c>
-      <c r="AA54" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AB54" s="5">
-        <v>1</v>
-      </c>
-      <c r="AC54" s="5">
-        <v>300</v>
-      </c>
-      <c r="AD54" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AE54" s="6">
-        <v>2</v>
-      </c>
-      <c r="AF54" s="5">
-        <v>240</v>
-      </c>
-      <c r="AG54" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AH54" s="6">
-        <v>1</v>
-      </c>
-      <c r="AI54" s="6">
-        <v>1</v>
-      </c>
-      <c r="AJ54" s="5">
-        <v>0.49</v>
-      </c>
-      <c r="AK54" s="5">
-        <v>109648</v>
-      </c>
-      <c r="AL54" s="5">
-        <v>53703</v>
-      </c>
-      <c r="AM54" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="AN54" s="3">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="55" spans="1:40">
-      <c r="A55" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="B55" s="5">
-        <v>178.7</v>
-      </c>
-      <c r="C55" s="5">
-        <v>4.8</v>
-      </c>
-      <c r="D55" s="5">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="E55" s="5">
-        <v>2139</v>
-      </c>
-      <c r="F55" s="5">
-        <v>1.17</v>
-      </c>
-      <c r="G55" s="5">
-        <v>40.200000000000003</v>
-      </c>
-      <c r="H55" s="5">
-        <v>17</v>
-      </c>
-      <c r="I55" s="5">
-        <v>11.4</v>
-      </c>
-      <c r="J55" s="5">
-        <v>346.75</v>
-      </c>
-      <c r="K55" s="6">
-        <v>240</v>
-      </c>
-      <c r="L55" s="6">
-        <v>300</v>
-      </c>
-      <c r="M55" s="6">
-        <v>130.66666670000001</v>
-      </c>
-      <c r="N55" s="5">
-        <v>1.55</v>
-      </c>
-      <c r="O55" s="5">
-        <v>2</v>
-      </c>
-      <c r="P55" s="6">
-        <v>242.5</v>
-      </c>
-      <c r="Q55" s="6">
-        <v>87.333333330000002</v>
-      </c>
-      <c r="R55" s="5">
-        <v>15.55</v>
-      </c>
-      <c r="S55" s="5">
-        <v>125</v>
-      </c>
-      <c r="T55" s="5">
-        <v>0.74</v>
-      </c>
-      <c r="U55" s="5">
-        <v>259.41666670000001</v>
-      </c>
-      <c r="V55" s="5">
-        <v>11</v>
-      </c>
-      <c r="W55" s="5">
-        <v>0</v>
-      </c>
-      <c r="X55" s="6">
-        <v>1</v>
-      </c>
-      <c r="Y55" s="6">
-        <v>3</v>
-      </c>
-      <c r="Z55" s="6">
-        <v>2</v>
-      </c>
-      <c r="AA55" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AB55" s="5">
-        <v>3.5</v>
-      </c>
-      <c r="AC55" s="5">
-        <v>160</v>
-      </c>
-      <c r="AD55" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AE55" s="6">
-        <v>2</v>
-      </c>
-      <c r="AF55" s="5">
-        <v>180.22499999999999</v>
-      </c>
-      <c r="AG55" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AH55" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="AI55" s="6">
-        <v>4</v>
-      </c>
-      <c r="AJ55" s="5">
-        <v>0.45</v>
-      </c>
-      <c r="AK55" s="5">
-        <v>338844</v>
-      </c>
-      <c r="AL55" s="5">
-        <v>151356</v>
-      </c>
-      <c r="AM55" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="AN55" s="3">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="56" spans="1:40">
-      <c r="A56" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="B56" s="5">
-        <v>952.428</v>
-      </c>
-      <c r="C56" s="5">
-        <v>10.6</v>
-      </c>
-      <c r="D56" s="5">
-        <v>4</v>
-      </c>
-      <c r="E56" s="5">
-        <v>4723</v>
-      </c>
-      <c r="F56" s="5">
-        <v>1.2549999999999999</v>
-      </c>
-      <c r="G56" s="5">
-        <v>147</v>
-      </c>
-      <c r="H56" s="5">
-        <v>15.66</v>
-      </c>
-      <c r="I56" s="5">
-        <v>23</v>
-      </c>
-      <c r="J56" s="5">
-        <v>699.58333330000005</v>
-      </c>
-      <c r="K56" s="6">
-        <v>430</v>
-      </c>
-      <c r="L56" s="6">
-        <v>639</v>
-      </c>
-      <c r="M56" s="6">
-        <v>134</v>
-      </c>
-      <c r="N56" s="5">
-        <v>1.5333333330000001</v>
-      </c>
-      <c r="O56" s="5">
-        <v>1</v>
-      </c>
-      <c r="P56" s="6">
-        <v>281.33333329999999</v>
-      </c>
-      <c r="Q56" s="6">
-        <v>121</v>
-      </c>
-      <c r="R56" s="5">
-        <v>43.96</v>
-      </c>
-      <c r="S56" s="5">
-        <v>500</v>
-      </c>
-      <c r="T56" s="5">
-        <v>1.47</v>
-      </c>
-      <c r="U56" s="5">
-        <v>578.58333330000005</v>
-      </c>
-      <c r="V56" s="5">
-        <v>10</v>
-      </c>
-      <c r="W56" s="5">
-        <v>27</v>
-      </c>
-      <c r="X56" s="6">
-        <v>1</v>
-      </c>
-      <c r="Y56" s="6">
-        <v>5</v>
-      </c>
-      <c r="Z56" s="6">
-        <v>2</v>
-      </c>
-      <c r="AA56" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AB56" s="5">
-        <v>3.5</v>
-      </c>
-      <c r="AC56" s="5">
-        <v>307</v>
-      </c>
-      <c r="AD56" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AE56" s="6">
-        <v>2</v>
-      </c>
-      <c r="AF56" s="5">
-        <v>457.15</v>
-      </c>
-      <c r="AG56" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AH56" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="AI56" s="6">
-        <v>1</v>
-      </c>
-      <c r="AJ56" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AK56" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AL56" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AM56" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="AN56" s="3">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="57" spans="1:40">
-      <c r="A57" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="B57" s="5">
-        <v>71.5</v>
-      </c>
-      <c r="C57" s="5">
-        <v>3.3450000000000002</v>
-      </c>
-      <c r="D57" s="5">
-        <v>1.1990000000000001</v>
-      </c>
-      <c r="E57" s="5">
-        <v>1568</v>
-      </c>
-      <c r="F57" s="5">
-        <v>1.21</v>
-      </c>
-      <c r="G57" s="5">
-        <v>30.4</v>
-      </c>
-      <c r="H57" s="5">
-        <v>14</v>
-      </c>
-      <c r="I57" s="5">
-        <v>21.4</v>
-      </c>
-      <c r="J57" s="5">
-        <v>650.91666669999995</v>
-      </c>
-      <c r="K57" s="6">
-        <v>240</v>
-      </c>
-      <c r="L57" s="6">
-        <v>274</v>
-      </c>
-      <c r="M57" s="6">
-        <v>110.33333330000001</v>
-      </c>
-      <c r="N57" s="5">
-        <v>1.6</v>
-      </c>
-      <c r="O57" s="5">
-        <v>1.5</v>
-      </c>
-      <c r="P57" s="6">
-        <v>330</v>
-      </c>
       <c r="Q57" s="6">
-        <v>45</v>
+        <v>109.25</v>
       </c>
       <c r="R57" s="5">
-        <v>8.4666666670000001</v>
-      </c>
-      <c r="S57" s="5" t="s">
-        <v>42</v>
+        <v>88.2</v>
+      </c>
+      <c r="S57" s="5">
+        <v>2696.5</v>
       </c>
       <c r="T57" s="5" t="s">
         <v>42</v>
       </c>
       <c r="U57" s="5">
-        <v>605.91666669999995</v>
+        <v>599.45833330000005</v>
       </c>
       <c r="V57" s="5">
-        <v>1</v>
-      </c>
-      <c r="W57" s="5" t="s">
-        <v>42</v>
+        <v>25.8</v>
+      </c>
+      <c r="W57" s="5">
+        <v>73.900000000000006</v>
       </c>
       <c r="X57" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y57" s="6">
         <v>4</v>
       </c>
       <c r="Z57" s="6">
-        <v>2</v>
-      </c>
-      <c r="AA57" s="5" t="s">
-        <v>42</v>
+        <v>1</v>
+      </c>
+      <c r="AA57" s="5">
+        <v>3.5</v>
       </c>
       <c r="AB57" s="5">
-        <v>5.5</v>
+        <v>2.8</v>
       </c>
       <c r="AC57" s="5">
-        <v>120</v>
+        <v>547.35</v>
       </c>
       <c r="AD57" s="5" t="s">
         <v>42</v>
@@ -7753,16 +7801,16 @@
         <v>2</v>
       </c>
       <c r="AF57" s="5">
-        <v>59.4</v>
+        <v>603.6</v>
       </c>
       <c r="AG57" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="AH57" s="6" t="s">
-        <v>42</v>
+      <c r="AH57" s="6">
+        <v>2</v>
       </c>
       <c r="AI57" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AJ57" s="5" t="s">
         <v>42</v>
@@ -7777,10 +7825,10 @@
         <v>42</v>
       </c>
       <c r="AN57" s="3">
-        <v>55</v>
+        <v>48</v>
       </c>
     </row>
-    <row r="58" spans="1:40">
+    <row r="58" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A58" s="4" t="s">
         <v>98</v>
       </c>
@@ -7902,7 +7950,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="59" spans="1:40">
+    <row r="59" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A59" s="4" t="s">
         <v>99</v>
       </c>
@@ -8024,7 +8072,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="60" spans="1:40">
+    <row r="60" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A60" s="4" t="s">
         <v>100</v>
       </c>
@@ -8146,7 +8194,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="61" spans="1:40">
+    <row r="61" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A61" s="4" t="s">
         <v>101</v>
       </c>
@@ -8268,7 +8316,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="62" spans="1:40">
+    <row r="62" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A62" s="4" t="s">
         <v>102</v>
       </c>
@@ -8390,7 +8438,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="63" spans="1:40">
+    <row r="63" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A63" s="4" t="s">
         <v>103</v>
       </c>
@@ -8512,7 +8560,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="64" spans="1:40">
+    <row r="64" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A64" s="4" t="s">
         <v>104</v>
       </c>
@@ -8634,7 +8682,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="65" spans="1:40">
+    <row r="65" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A65" s="4" t="s">
         <v>105</v>
       </c>
@@ -8756,7 +8804,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="66" spans="1:40">
+    <row r="66" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A66" s="4" t="s">
         <v>106</v>
       </c>
@@ -8878,7 +8926,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="67" spans="1:40">
+    <row r="67" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A67" s="4" t="s">
         <v>107</v>
       </c>
@@ -9000,7 +9048,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="68" spans="1:40">
+    <row r="68" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A68" s="4" t="s">
         <v>108</v>
       </c>
@@ -9122,7 +9170,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="69" spans="1:40">
+    <row r="69" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A69" s="4" t="s">
         <v>109</v>
       </c>
@@ -9244,7 +9292,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="70" spans="1:40">
+    <row r="70" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A70" s="4" t="s">
         <v>110</v>
       </c>
@@ -9366,7 +9414,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="71" spans="1:40">
+    <row r="71" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A71" s="4" t="s">
         <v>111</v>
       </c>
@@ -9488,7 +9536,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="72" spans="1:40">
+    <row r="72" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A72" s="4" t="s">
         <v>112</v>
       </c>
@@ -9610,7 +9658,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="73" spans="1:40">
+    <row r="73" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A73" s="4" t="s">
         <v>113</v>
       </c>
@@ -9732,7 +9780,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="74" spans="1:40">
+    <row r="74" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A74" s="4" t="s">
         <v>114</v>
       </c>
@@ -9854,7 +9902,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="75" spans="1:40">
+    <row r="75" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A75" s="4" t="s">
         <v>115</v>
       </c>
@@ -9976,7 +10024,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="76" spans="1:40">
+    <row r="76" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A76" s="4" t="s">
         <v>116</v>
       </c>
@@ -10098,7 +10146,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="77" spans="1:40">
+    <row r="77" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A77" s="4" t="s">
         <v>117</v>
       </c>
@@ -10220,7 +10268,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="78" spans="1:40">
+    <row r="78" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A78" s="4" t="s">
         <v>118</v>
       </c>
@@ -10342,7 +10390,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="79" spans="1:40">
+    <row r="79" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A79" s="4" t="s">
         <v>119</v>
       </c>
@@ -10464,7 +10512,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="80" spans="1:40">
+    <row r="80" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A80" s="4" t="s">
         <v>120</v>
       </c>
@@ -10586,7 +10634,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="81" spans="1:40">
+    <row r="81" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A81" s="4" t="s">
         <v>121</v>
       </c>
@@ -10708,7 +10756,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="82" spans="1:40">
+    <row r="82" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A82" s="4" t="s">
         <v>122</v>
       </c>
@@ -10830,7 +10878,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="83" spans="1:40">
+    <row r="83" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A83" s="4" t="s">
         <v>123</v>
       </c>
@@ -10952,7 +11000,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="84" spans="1:40">
+    <row r="84" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A84" s="4" t="s">
         <v>124</v>
       </c>
@@ -11074,7 +11122,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="85" spans="1:40">
+    <row r="85" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A85" s="4" t="s">
         <v>125</v>
       </c>
@@ -11196,7 +11244,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="86" spans="1:40">
+    <row r="86" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A86" s="4" t="s">
         <v>126</v>
       </c>
@@ -11318,7 +11366,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="87" spans="1:40">
+    <row r="87" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A87" s="4" t="s">
         <v>127</v>
       </c>
@@ -11440,7 +11488,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="88" spans="1:40">
+    <row r="88" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A88" s="4" t="s">
         <v>128</v>
       </c>
@@ -11562,7 +11610,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="89" spans="1:40">
+    <row r="89" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A89" s="4" t="s">
         <v>129</v>
       </c>
@@ -11684,7 +11732,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="90" spans="1:40">
+    <row r="90" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A90" s="4" t="s">
         <v>130</v>
       </c>
@@ -11806,7 +11854,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="91" spans="1:40">
+    <row r="91" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A91" s="4" t="s">
         <v>131</v>
       </c>
@@ -11928,7 +11976,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="92" spans="1:40">
+    <row r="92" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A92" s="4" t="s">
         <v>132</v>
       </c>
@@ -12050,7 +12098,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="93" spans="1:40">
+    <row r="93" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A93" s="4" t="s">
         <v>133</v>
       </c>
@@ -12172,7 +12220,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="94" spans="1:40">
+    <row r="94" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A94" s="4" t="s">
         <v>134</v>
       </c>
@@ -12294,7 +12342,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="95" spans="1:40">
+    <row r="95" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A95" s="4" t="s">
         <v>135</v>
       </c>
@@ -12416,7 +12464,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="96" spans="1:40">
+    <row r="96" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A96" s="4" t="s">
         <v>136</v>
       </c>
@@ -12538,7 +12586,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="97" spans="1:40">
+    <row r="97" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A97" s="4" t="s">
         <v>137</v>
       </c>
@@ -12660,7 +12708,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="98" spans="1:40">
+    <row r="98" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A98" s="4" t="s">
         <v>138</v>
       </c>
@@ -12782,7 +12830,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="99" spans="1:40">
+    <row r="99" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A99" s="4" t="s">
         <v>139</v>
       </c>
@@ -12904,7 +12952,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="100" spans="1:40">
+    <row r="100" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A100" s="4" t="s">
         <v>140</v>
       </c>
@@ -13026,7 +13074,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="101" spans="1:40">
+    <row r="101" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A101" s="4" t="s">
         <v>141</v>
       </c>
@@ -13148,7 +13196,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="102" spans="1:40">
+    <row r="102" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A102" s="4" t="s">
         <v>142</v>
       </c>
@@ -13270,7 +13318,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="103" spans="1:40">
+    <row r="103" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A103" s="4" t="s">
         <v>143</v>
       </c>
@@ -13392,7 +13440,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="104" spans="1:40">
+    <row r="104" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A104" s="4" t="s">
         <v>144</v>
       </c>
@@ -13514,7 +13562,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="105" spans="1:40" ht="16">
+    <row r="105" spans="1:40" ht="19" x14ac:dyDescent="0.2">
       <c r="A105" s="4" t="s">
         <v>145</v>
       </c>
@@ -13558,7 +13606,7 @@
       <c r="AM105" s="6"/>
       <c r="AN105" s="3"/>
     </row>
-    <row r="106" spans="1:40">
+    <row r="106" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A106" s="4" t="s">
         <v>146</v>
       </c>
@@ -13603,7 +13651,50 @@
       <c r="AN106" s="3"/>
     </row>
   </sheetData>
+  <autoFilter ref="A2:AN106" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="4">
+      <filters blank="1">
+        <filter val="12207.00"/>
+        <filter val="1221.00"/>
+        <filter val="13170.00"/>
+        <filter val="15293.00"/>
+        <filter val="15541.00"/>
+        <filter val="1568.00"/>
+        <filter val="20114.00"/>
+        <filter val="2139.00"/>
+        <filter val="22127.00"/>
+        <filter val="26427.00"/>
+        <filter val="291592.00"/>
+        <filter val="2938.00"/>
+        <filter val="3282.00"/>
+        <filter val="341444.00"/>
+        <filter val="3524.00"/>
+        <filter val="4371.00"/>
+        <filter val="4443.00"/>
+        <filter val="4723.00"/>
+        <filter val="4813.00"/>
+        <filter val="48763.00"/>
+        <filter val="50906.00"/>
+        <filter val="5883.00"/>
+        <filter val="5894.00"/>
+        <filter val="6.19"/>
+        <filter val="63482.00"/>
+        <filter val="6476.00"/>
+        <filter val="65800.00"/>
+        <filter val="65873.00"/>
+        <filter val="6683.00"/>
+        <filter val="68733.00"/>
+        <filter val="740.00"/>
+        <filter val="77141.00"/>
+        <filter val="9950.00"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A12:AN57">
+    <sortCondition ref="A2:A57"/>
+  </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <extLst>
     <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
       <mx:PLV Mode="0" OnePage="0" WScale="0"/>
@@ -13613,8 +13704,28 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d42a73f51a03135be35f4acb272f8cf1">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2ea21b36c10eaa86a5cb337ec7f4e0a6" ns2:_="" ns3:_="">
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
     <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
     <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
     <xsd:element name="properties">
@@ -13867,34 +13978,31 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6173295B-D545-4916-A49F-4289A8766507}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{07EB4ABC-2807-46D9-B328-AF7D2B4EFA60}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1DF43C26-8B78-4041-9B7A-975567309F97}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1DF43C26-8B78-4041-9B7A-975567309F97}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{07EB4ABC-2807-46D9-B328-AF7D2B4EFA60}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{326B22DB-7DC3-4CEA-9FB7-537787EED270}"/>
 </file>